--- a/Advanced Reactor Materials/Fall2025/grading.xlsx
+++ b/Advanced Reactor Materials/Fall2025/grading.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/beelbw/projects/TEACHING/Advanced Reactor Materials/Fall2025/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CE80106-AE84-F24B-BB6D-DD59151A2AC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A1E2141-32C2-024B-A33E-E669F034FF1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="24260" yWindow="8540" windowWidth="24220" windowHeight="17440" xr2:uid="{4E6CEA4E-2509-754B-9890-44C713F10933}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="22">
   <si>
     <t>Roster</t>
   </si>
@@ -99,6 +99,9 @@
   </si>
   <si>
     <t>Grade Values</t>
+  </si>
+  <si>
+    <t>Cecilia Harrison</t>
   </si>
 </sst>
 </file>
@@ -470,7 +473,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7A9E859-0099-8A4F-9892-6572C8559B21}">
-  <dimension ref="B2:N20"/>
+  <dimension ref="B2:N21"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="20.1640625" customWidth="1"/>
@@ -548,11 +551,11 @@
         <v>1</v>
       </c>
       <c r="I6">
-        <f>(C6+C$19)*C$3</f>
+        <f>(C6+C$20)*C$3</f>
         <v>0</v>
       </c>
       <c r="J6">
-        <f t="shared" ref="J6:M6" si="0">(D6+D$19)*D$3</f>
+        <f t="shared" ref="J6:M6" si="0">(D6+D$20)*D$3</f>
         <v>0</v>
       </c>
       <c r="K6">
@@ -577,290 +580,319 @@
         <v>2</v>
       </c>
       <c r="I7">
-        <f t="shared" ref="I7:I16" si="1">(C7+C$19)*C$3</f>
+        <f>(C7+C$20)*C$3</f>
         <v>0</v>
       </c>
       <c r="J7">
-        <f t="shared" ref="J7:J16" si="2">(D7+D$19)*D$3</f>
+        <f>(D7+D$20)*D$3</f>
         <v>0</v>
       </c>
       <c r="K7">
-        <f t="shared" ref="K7:K16" si="3">(E7+E$19)*E$3</f>
+        <f>(E7+E$20)*E$3</f>
         <v>0</v>
       </c>
       <c r="L7">
-        <f t="shared" ref="L7:L16" si="4">(F7+F$19)*F$3</f>
+        <f>(F7+F$20)*F$3</f>
         <v>0</v>
       </c>
       <c r="M7">
-        <f t="shared" ref="M7:M16" si="5">(G7+G$19)*G$3</f>
+        <f>(G7+G$20)*G$3</f>
         <v>0</v>
       </c>
       <c r="N7">
-        <f t="shared" ref="N7:N16" si="6">SUM(I7:M7)</f>
+        <f t="shared" ref="N7:N17" si="1">SUM(I7:M7)</f>
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B8" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="I8">
-        <f t="shared" si="1"/>
+        <f>(C8+C$20)*C$3</f>
         <v>0</v>
       </c>
       <c r="J8">
-        <f t="shared" si="2"/>
+        <f>(D8+D$20)*D$3</f>
         <v>0</v>
       </c>
       <c r="K8">
-        <f t="shared" si="3"/>
+        <f>(E8+E$20)*E$3</f>
         <v>0</v>
       </c>
       <c r="L8">
-        <f t="shared" si="4"/>
+        <f>(F8+F$20)*F$3</f>
         <v>0</v>
       </c>
       <c r="M8">
-        <f t="shared" si="5"/>
+        <f>(G8+G$20)*G$3</f>
         <v>0</v>
       </c>
       <c r="N8">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="N8" si="2">SUM(I8:M8)</f>
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B9" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I9">
+        <f>(C9+C$20)*C$3</f>
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <f>(D9+D$20)*D$3</f>
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <f>(E9+E$20)*E$3</f>
+        <v>0</v>
+      </c>
+      <c r="L9">
+        <f>(F9+F$20)*F$3</f>
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <f>(G9+G$20)*G$3</f>
+        <v>0</v>
+      </c>
+      <c r="N9">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J9">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K9">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="L9">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M9">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="N9">
-        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B10" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I10">
+        <f>(C10+C$20)*C$3</f>
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <f>(D10+D$20)*D$3</f>
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <f>(E10+E$20)*E$3</f>
+        <v>0</v>
+      </c>
+      <c r="L10">
+        <f>(F10+F$20)*F$3</f>
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <f>(G10+G$20)*G$3</f>
+        <v>0</v>
+      </c>
+      <c r="N10">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J10">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K10">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="L10">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M10">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="N10">
-        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B11" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I11">
+        <f>(C11+C$20)*C$3</f>
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <f>(D11+D$20)*D$3</f>
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <f>(E11+E$20)*E$3</f>
+        <v>0</v>
+      </c>
+      <c r="L11">
+        <f>(F11+F$20)*F$3</f>
+        <v>0</v>
+      </c>
+      <c r="M11">
+        <f>(G11+G$20)*G$3</f>
+        <v>0</v>
+      </c>
+      <c r="N11">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J11">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K11">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="L11">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M11">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="N11">
-        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B12" t="s">
+        <v>9</v>
+      </c>
+      <c r="I12">
+        <f>(C12+C$20)*C$3</f>
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <f>(D12+D$20)*D$3</f>
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <f>(E12+E$20)*E$3</f>
+        <v>0</v>
+      </c>
+      <c r="L12">
+        <f>(F12+F$20)*F$3</f>
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <f>(G12+G$20)*G$3</f>
+        <v>0</v>
+      </c>
+      <c r="N12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B13" t="s">
         <v>10</v>
       </c>
-      <c r="I12">
+      <c r="I13">
+        <f>(C13+C$20)*C$3</f>
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <f>(D13+D$20)*D$3</f>
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <f>(E13+E$20)*E$3</f>
+        <v>0</v>
+      </c>
+      <c r="L13">
+        <f>(F13+F$20)*F$3</f>
+        <v>0</v>
+      </c>
+      <c r="M13">
+        <f>(G13+G$20)*G$3</f>
+        <v>0</v>
+      </c>
+      <c r="N13">
         <f t="shared" si="1"/>
         <v>0</v>
-      </c>
-      <c r="J12">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K12">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="L12">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M12">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="N12">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B14" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="15" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B15" t="s">
-        <v>4</v>
-      </c>
-      <c r="I15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J15">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K15">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="L15">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M15">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="N15">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B16" t="s">
+        <v>4</v>
+      </c>
+      <c r="I16">
+        <f>(C16+C$20)*C$3</f>
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <f>(D16+D$20)*D$3</f>
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <f>(E16+E$20)*E$3</f>
+        <v>0</v>
+      </c>
+      <c r="L16">
+        <f>(F16+F$20)*F$3</f>
+        <v>0</v>
+      </c>
+      <c r="M16">
+        <f>(G16+G$20)*G$3</f>
+        <v>0</v>
+      </c>
+      <c r="N16">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B17" t="s">
         <v>7</v>
       </c>
-      <c r="I16">
+      <c r="I17">
+        <f>(C17+C$20)*C$3</f>
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <f>(D17+D$20)*D$3</f>
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <f>(E17+E$20)*E$3</f>
+        <v>0</v>
+      </c>
+      <c r="L17">
+        <f>(F17+F$20)*F$3</f>
+        <v>0</v>
+      </c>
+      <c r="M17">
+        <f>(G17+G$20)*G$3</f>
+        <v>0</v>
+      </c>
+      <c r="N17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J16">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K16">
+    </row>
+    <row r="19" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B19" t="s">
+        <v>16</v>
+      </c>
+      <c r="C19" t="e">
+        <f>AVERAGE(C6:C17)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D19" t="e">
+        <f t="shared" ref="D19:G19" si="3">AVERAGE(D6:D17)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E19" t="e">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="L16">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F19" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G19" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="20" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B20" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="21" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B21" t="s">
+        <v>18</v>
+      </c>
+      <c r="C21" t="e">
+        <f>C19+C20</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D21" t="e">
+        <f t="shared" ref="D21:G21" si="4">D19+D20</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E21" t="e">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M16">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="N16">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B18" t="s">
-        <v>16</v>
-      </c>
-      <c r="C18" t="e">
-        <f>AVERAGE(C6:C16)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="D18" t="e">
-        <f t="shared" ref="D18:G18" si="7">AVERAGE(D6:D16)</f>
+      <c r="F21" t="e">
+        <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="E18" t="e">
-        <f t="shared" si="7"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F18" t="e">
-        <f t="shared" si="7"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G18" t="e">
-        <f t="shared" si="7"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B19" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="20" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B20" t="s">
-        <v>18</v>
-      </c>
-      <c r="C20" t="e">
-        <f>C18+C19</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="D20" t="e">
-        <f t="shared" ref="D20:G20" si="8">D18+D19</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E20" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F20" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G20" t="e">
-        <f t="shared" si="8"/>
+      <c r="G21" t="e">
+        <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
     </row>

--- a/Advanced Reactor Materials/Fall2025/grading.xlsx
+++ b/Advanced Reactor Materials/Fall2025/grading.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10905"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/beelbw/projects/TEACHING/Advanced Reactor Materials/Fall2025/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A1E2141-32C2-024B-A33E-E669F034FF1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C5E1018-1E6D-F547-9648-99489A286995}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="24260" yWindow="8540" windowWidth="24220" windowHeight="17440" xr2:uid="{4E6CEA4E-2509-754B-9890-44C713F10933}"/>
+    <workbookView xWindow="5120" yWindow="8740" windowWidth="24220" windowHeight="17440" xr2:uid="{4E6CEA4E-2509-754B-9890-44C713F10933}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="22">
   <si>
     <t>Roster</t>
   </si>
@@ -65,9 +65,6 @@
     <t>Kyle Holloway</t>
   </si>
   <si>
-    <t>Nermeen Elamrawy</t>
-  </si>
-  <si>
     <t>Rashed Almasri</t>
   </si>
   <si>
@@ -102,6 +99,9 @@
   </si>
   <si>
     <t>Cecilia Harrison</t>
+  </si>
+  <si>
+    <t>sum</t>
   </si>
 </sst>
 </file>
@@ -473,7 +473,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7A9E859-0099-8A4F-9892-6572C8559B21}">
-  <dimension ref="B2:N21"/>
+  <dimension ref="B2:N36"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="20.1640625" customWidth="1"/>
@@ -483,7 +483,7 @@
   <sheetData>
     <row r="2" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="2:14" x14ac:dyDescent="0.2">
@@ -505,7 +505,7 @@
     </row>
     <row r="4" spans="2:14" x14ac:dyDescent="0.2">
       <c r="I4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="2:14" x14ac:dyDescent="0.2">
@@ -513,37 +513,37 @@
         <v>0</v>
       </c>
       <c r="C5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" t="s">
         <v>11</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>12</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>13</v>
       </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
         <v>14</v>
       </c>
-      <c r="G5" t="s">
-        <v>15</v>
-      </c>
       <c r="I5" t="s">
+        <v>10</v>
+      </c>
+      <c r="J5" t="s">
         <v>11</v>
       </c>
-      <c r="J5" t="s">
+      <c r="K5" t="s">
         <v>12</v>
       </c>
-      <c r="K5" t="s">
+      <c r="L5" t="s">
         <v>13</v>
       </c>
-      <c r="L5" t="s">
+      <c r="M5" t="s">
         <v>14</v>
       </c>
-      <c r="M5" t="s">
-        <v>15</v>
-      </c>
       <c r="N5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6" spans="2:14" x14ac:dyDescent="0.2">
@@ -551,11 +551,11 @@
         <v>1</v>
       </c>
       <c r="I6">
-        <f>(C6+C$20)*C$3</f>
+        <f t="shared" ref="I6:M12" si="0">(C6+C$19)*C$3</f>
         <v>0</v>
       </c>
       <c r="J6">
-        <f t="shared" ref="J6:M6" si="0">(D6+D$20)*D$3</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K6">
@@ -580,52 +580,52 @@
         <v>2</v>
       </c>
       <c r="I7">
-        <f>(C7+C$20)*C$3</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J7">
-        <f>(D7+D$20)*D$3</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K7">
-        <f>(E7+E$20)*E$3</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="L7">
-        <f>(F7+F$20)*F$3</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="M7">
-        <f>(G7+G$20)*G$3</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="N7">
-        <f t="shared" ref="N7:N17" si="1">SUM(I7:M7)</f>
+        <f t="shared" ref="N7:N16" si="1">SUM(I7:M7)</f>
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I8">
-        <f>(C8+C$20)*C$3</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J8">
-        <f>(D8+D$20)*D$3</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K8">
-        <f>(E8+E$20)*E$3</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="L8">
-        <f>(F8+F$20)*F$3</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="M8">
-        <f>(G8+G$20)*G$3</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="N8">
@@ -638,23 +638,23 @@
         <v>5</v>
       </c>
       <c r="I9">
-        <f>(C9+C$20)*C$3</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J9">
-        <f>(D9+D$20)*D$3</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K9">
-        <f>(E9+E$20)*E$3</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="L9">
-        <f>(F9+F$20)*F$3</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="M9">
-        <f>(G9+G$20)*G$3</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="N9">
@@ -667,23 +667,23 @@
         <v>6</v>
       </c>
       <c r="I10">
-        <f>(C10+C$20)*C$3</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J10">
-        <f>(D10+D$20)*D$3</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K10">
-        <f>(E10+E$20)*E$3</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="L10">
-        <f>(F10+F$20)*F$3</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="M10">
-        <f>(G10+G$20)*G$3</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="N10">
@@ -696,23 +696,23 @@
         <v>8</v>
       </c>
       <c r="I11">
-        <f>(C11+C$20)*C$3</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J11">
-        <f>(D11+D$20)*D$3</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K11">
-        <f>(E11+E$20)*E$3</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="L11">
-        <f>(F11+F$20)*F$3</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="M11">
-        <f>(G11+G$20)*G$3</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="N11">
@@ -725,23 +725,23 @@
         <v>9</v>
       </c>
       <c r="I12">
-        <f>(C12+C$20)*C$3</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J12">
-        <f>(D12+D$20)*D$3</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K12">
-        <f>(E12+E$20)*E$3</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="L12">
-        <f>(F12+F$20)*F$3</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="M12">
-        <f>(G12+G$20)*G$3</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="N12">
@@ -749,62 +749,62 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B13" t="s">
-        <v>10</v>
-      </c>
-      <c r="I13">
-        <f>(C13+C$20)*C$3</f>
-        <v>0</v>
-      </c>
-      <c r="J13">
-        <f>(D13+D$20)*D$3</f>
-        <v>0</v>
-      </c>
-      <c r="K13">
-        <f>(E13+E$20)*E$3</f>
-        <v>0</v>
-      </c>
-      <c r="L13">
-        <f>(F13+F$20)*F$3</f>
-        <v>0</v>
-      </c>
-      <c r="M13">
-        <f>(G13+G$20)*G$3</f>
-        <v>0</v>
-      </c>
-      <c r="N13">
-        <f t="shared" si="1"/>
-        <v>0</v>
+    <row r="14" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B14" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="15" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B15" t="s">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="I15">
+        <f t="shared" ref="I15:M16" si="3">(C15+C$19)*C$3</f>
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L15">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M15">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="N15">
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B16" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I16">
-        <f>(C16+C$20)*C$3</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J16">
-        <f>(D16+D$20)*D$3</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="K16">
-        <f>(E16+E$20)*E$3</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L16">
-        <f>(F16+F$20)*F$3</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="M16">
-        <f>(G16+G$20)*G$3</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N16">
@@ -812,88 +812,249 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B17" t="s">
-        <v>7</v>
-      </c>
-      <c r="I17">
-        <f>(C17+C$20)*C$3</f>
-        <v>0</v>
-      </c>
-      <c r="J17">
-        <f>(D17+D$20)*D$3</f>
-        <v>0</v>
-      </c>
-      <c r="K17">
-        <f>(E17+E$20)*E$3</f>
-        <v>0</v>
-      </c>
-      <c r="L17">
-        <f>(F17+F$20)*F$3</f>
-        <v>0</v>
-      </c>
-      <c r="M17">
-        <f>(G17+G$20)*G$3</f>
-        <v>0</v>
-      </c>
-      <c r="N17">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B18" t="s">
+        <v>15</v>
+      </c>
+      <c r="C18" t="e">
+        <f>AVERAGE(C6:C16)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D18" t="e">
+        <f>AVERAGE(D6:D16)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E18" t="e">
+        <f>AVERAGE(E6:E16)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F18" t="e">
+        <f>AVERAGE(F6:F16)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G18" t="e">
+        <f>AVERAGE(G6:G16)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="19" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B19" t="s">
         <v>16</v>
       </c>
-      <c r="C19" t="e">
-        <f>AVERAGE(C6:C17)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="D19" t="e">
-        <f t="shared" ref="D19:G19" si="3">AVERAGE(D6:D17)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E19" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F19" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G19" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="20" spans="2:14" x14ac:dyDescent="0.2">
+    </row>
+    <row r="20" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B20" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="21" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B21" t="s">
-        <v>18</v>
-      </c>
-      <c r="C21" t="e">
-        <f>C19+C20</f>
+      <c r="C20" t="e">
+        <f>C18+C19</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="D21" t="e">
-        <f t="shared" ref="D21:G21" si="4">D19+D20</f>
+      <c r="D20" t="e">
+        <f t="shared" ref="D20:G20" si="4">D18+D19</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E21" t="e">
+      <c r="E20" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F21" t="e">
+      <c r="F20" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="G21" t="e">
+      <c r="G20" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="25" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B25" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" t="s">
+        <v>18</v>
+      </c>
+      <c r="D25" t="s">
+        <v>1</v>
+      </c>
+      <c r="E25" t="s">
+        <v>2</v>
+      </c>
+      <c r="F25" t="s">
+        <v>20</v>
+      </c>
+      <c r="G25" t="s">
+        <v>5</v>
+      </c>
+      <c r="H25" t="s">
+        <v>6</v>
+      </c>
+      <c r="I25" t="s">
+        <v>8</v>
+      </c>
+      <c r="J25" t="s">
+        <v>9</v>
+      </c>
+      <c r="K25" t="s">
+        <v>4</v>
+      </c>
+      <c r="L25" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="26" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B26">
+        <v>1</v>
+      </c>
+      <c r="C26">
+        <v>8</v>
+      </c>
+      <c r="D26">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="27" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B27">
+        <v>2</v>
+      </c>
+      <c r="C27">
+        <v>10</v>
+      </c>
+      <c r="D27">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="28" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B28">
+        <v>3</v>
+      </c>
+      <c r="C28">
+        <v>10</v>
+      </c>
+      <c r="D28">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="29" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B29">
+        <v>4</v>
+      </c>
+      <c r="C29">
+        <v>15</v>
+      </c>
+      <c r="D29">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="30" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B30">
+        <v>5</v>
+      </c>
+      <c r="C30">
+        <v>10</v>
+      </c>
+      <c r="D30">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="31" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B31">
+        <v>6</v>
+      </c>
+      <c r="C31">
+        <v>10</v>
+      </c>
+      <c r="D31">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="32" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B32">
+        <v>7</v>
+      </c>
+      <c r="C32">
+        <v>15</v>
+      </c>
+      <c r="D32">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B33">
+        <v>8</v>
+      </c>
+      <c r="C33">
+        <v>9</v>
+      </c>
+      <c r="D33">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B34">
+        <v>9</v>
+      </c>
+      <c r="C34">
+        <v>5</v>
+      </c>
+      <c r="D34">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B35">
+        <v>10</v>
+      </c>
+      <c r="C35">
+        <v>8</v>
+      </c>
+      <c r="D35">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B36" t="s">
+        <v>21</v>
+      </c>
+      <c r="C36">
+        <f>SUM(C26:C35)</f>
+        <v>100</v>
+      </c>
+      <c r="D36">
+        <f t="shared" ref="D36:L36" si="5">SUM(D26:D35)</f>
+        <v>97</v>
+      </c>
+      <c r="E36">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="F36">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="G36">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="H36">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="I36">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="K36">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="L36">
+        <f t="shared" si="5"/>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Advanced Reactor Materials/Fall2025/grading.xlsx
+++ b/Advanced Reactor Materials/Fall2025/grading.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10905"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10913"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/beelbw/projects/TEACHING/Advanced Reactor Materials/Fall2025/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C5E1018-1E6D-F547-9648-99489A286995}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0806182-D537-BD45-8EF0-7653B7F6AC91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5120" yWindow="8740" windowWidth="24220" windowHeight="17440" xr2:uid="{4E6CEA4E-2509-754B-9890-44C713F10933}"/>
   </bookViews>
@@ -108,6 +108,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+  </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
@@ -137,8 +140,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -550,9 +554,12 @@
       <c r="B6" t="s">
         <v>1</v>
       </c>
+      <c r="C6">
+        <v>95</v>
+      </c>
       <c r="I6">
         <f t="shared" ref="I6:M12" si="0">(C6+C$19)*C$3</f>
-        <v>0</v>
+        <v>19.400000000000002</v>
       </c>
       <c r="J6">
         <f t="shared" si="0"/>
@@ -572,16 +579,19 @@
       </c>
       <c r="N6">
         <f>SUM(I6:M6)</f>
-        <v>0</v>
+        <v>19.400000000000002</v>
       </c>
     </row>
     <row r="7" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B7" t="s">
         <v>2</v>
       </c>
+      <c r="C7">
+        <v>94</v>
+      </c>
       <c r="I7">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>19.200000000000003</v>
       </c>
       <c r="J7">
         <f t="shared" si="0"/>
@@ -601,16 +611,19 @@
       </c>
       <c r="N7">
         <f t="shared" ref="N7:N16" si="1">SUM(I7:M7)</f>
-        <v>0</v>
+        <v>19.200000000000003</v>
       </c>
     </row>
     <row r="8" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B8" t="s">
         <v>20</v>
       </c>
+      <c r="C8">
+        <v>89</v>
+      </c>
       <c r="I8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>18.2</v>
       </c>
       <c r="J8">
         <f t="shared" si="0"/>
@@ -630,16 +643,19 @@
       </c>
       <c r="N8">
         <f t="shared" ref="N8" si="2">SUM(I8:M8)</f>
-        <v>0</v>
+        <v>18.2</v>
       </c>
     </row>
     <row r="9" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B9" t="s">
         <v>5</v>
       </c>
+      <c r="C9">
+        <v>84</v>
+      </c>
       <c r="I9">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>17.2</v>
       </c>
       <c r="J9">
         <f t="shared" si="0"/>
@@ -659,16 +675,19 @@
       </c>
       <c r="N9">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>17.2</v>
       </c>
     </row>
     <row r="10" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B10" t="s">
         <v>6</v>
       </c>
+      <c r="C10">
+        <v>74</v>
+      </c>
       <c r="I10">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>15.200000000000001</v>
       </c>
       <c r="J10">
         <f t="shared" si="0"/>
@@ -688,16 +707,19 @@
       </c>
       <c r="N10">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>15.200000000000001</v>
       </c>
     </row>
     <row r="11" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B11" t="s">
         <v>8</v>
       </c>
+      <c r="C11">
+        <v>90</v>
+      </c>
       <c r="I11">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>18.400000000000002</v>
       </c>
       <c r="J11">
         <f t="shared" si="0"/>
@@ -717,16 +739,19 @@
       </c>
       <c r="N11">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>18.400000000000002</v>
       </c>
     </row>
     <row r="12" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B12" t="s">
         <v>9</v>
       </c>
+      <c r="C12">
+        <v>91</v>
+      </c>
       <c r="I12">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>18.600000000000001</v>
       </c>
       <c r="J12">
         <f t="shared" si="0"/>
@@ -746,7 +771,7 @@
       </c>
       <c r="N12">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>18.600000000000001</v>
       </c>
     </row>
     <row r="14" spans="2:14" x14ac:dyDescent="0.2">
@@ -758,9 +783,12 @@
       <c r="B15" t="s">
         <v>4</v>
       </c>
+      <c r="C15">
+        <v>97</v>
+      </c>
       <c r="I15">
         <f t="shared" ref="I15:M16" si="3">(C15+C$19)*C$3</f>
-        <v>0</v>
+        <v>19.8</v>
       </c>
       <c r="J15">
         <f t="shared" si="3"/>
@@ -780,16 +808,19 @@
       </c>
       <c r="N15">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>19.8</v>
       </c>
     </row>
     <row r="16" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B16" t="s">
         <v>7</v>
       </c>
+      <c r="C16">
+        <v>83</v>
+      </c>
       <c r="I16">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="J16">
         <f t="shared" si="3"/>
@@ -809,30 +840,30 @@
       </c>
       <c r="N16">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B18" t="s">
         <v>15</v>
       </c>
-      <c r="C18" t="e">
+      <c r="C18" s="1">
         <f>AVERAGE(C6:C16)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="D18" t="e">
+        <v>88.555555555555557</v>
+      </c>
+      <c r="D18" s="1" t="e">
         <f>AVERAGE(D6:D16)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E18" t="e">
+      <c r="E18" s="1" t="e">
         <f>AVERAGE(E6:E16)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="F18" t="e">
+      <c r="F18" s="1" t="e">
         <f>AVERAGE(F6:F16)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G18" t="e">
+      <c r="G18" s="1" t="e">
         <f>AVERAGE(G6:G16)</f>
         <v>#DIV/0!</v>
       </c>
@@ -841,28 +872,31 @@
       <c r="B19" t="s">
         <v>16</v>
       </c>
+      <c r="C19">
+        <v>2</v>
+      </c>
     </row>
     <row r="20" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B20" t="s">
         <v>17</v>
       </c>
-      <c r="C20" t="e">
+      <c r="C20" s="1">
         <f>C18+C19</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="D20" t="e">
+        <v>90.555555555555557</v>
+      </c>
+      <c r="D20" s="1" t="e">
         <f t="shared" ref="D20:G20" si="4">D18+D19</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E20" t="e">
+      <c r="E20" s="1" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F20" t="e">
+      <c r="F20" s="1" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="G20" t="e">
+      <c r="G20" s="1" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
@@ -910,6 +944,30 @@
         <v>8</v>
       </c>
       <c r="D26">
+        <v>7</v>
+      </c>
+      <c r="E26">
+        <v>8</v>
+      </c>
+      <c r="F26">
+        <v>7</v>
+      </c>
+      <c r="G26">
+        <v>7</v>
+      </c>
+      <c r="H26">
+        <v>7</v>
+      </c>
+      <c r="I26">
+        <v>8</v>
+      </c>
+      <c r="J26">
+        <v>8</v>
+      </c>
+      <c r="K26">
+        <v>8</v>
+      </c>
+      <c r="L26">
         <v>8</v>
       </c>
     </row>
@@ -923,6 +981,30 @@
       <c r="D27">
         <v>10</v>
       </c>
+      <c r="E27">
+        <v>10</v>
+      </c>
+      <c r="F27">
+        <v>10</v>
+      </c>
+      <c r="G27">
+        <v>10</v>
+      </c>
+      <c r="H27">
+        <v>10</v>
+      </c>
+      <c r="I27">
+        <v>10</v>
+      </c>
+      <c r="J27">
+        <v>9</v>
+      </c>
+      <c r="K27">
+        <v>10</v>
+      </c>
+      <c r="L27">
+        <v>9</v>
+      </c>
     </row>
     <row r="28" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B28">
@@ -934,6 +1016,30 @@
       <c r="D28">
         <v>10</v>
       </c>
+      <c r="E28">
+        <v>10</v>
+      </c>
+      <c r="F28">
+        <v>10</v>
+      </c>
+      <c r="G28">
+        <v>10</v>
+      </c>
+      <c r="H28">
+        <v>7</v>
+      </c>
+      <c r="I28">
+        <v>10</v>
+      </c>
+      <c r="J28">
+        <v>10</v>
+      </c>
+      <c r="K28">
+        <v>10</v>
+      </c>
+      <c r="L28">
+        <v>8</v>
+      </c>
     </row>
     <row r="29" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B29">
@@ -945,6 +1051,30 @@
       <c r="D29">
         <v>15</v>
       </c>
+      <c r="E29">
+        <v>14</v>
+      </c>
+      <c r="F29">
+        <v>14</v>
+      </c>
+      <c r="G29">
+        <v>12</v>
+      </c>
+      <c r="H29">
+        <v>12</v>
+      </c>
+      <c r="I29">
+        <v>13</v>
+      </c>
+      <c r="J29">
+        <v>14</v>
+      </c>
+      <c r="K29">
+        <v>15</v>
+      </c>
+      <c r="L29">
+        <v>14</v>
+      </c>
     </row>
     <row r="30" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B30">
@@ -956,6 +1086,30 @@
       <c r="D30">
         <v>9</v>
       </c>
+      <c r="E30">
+        <v>8</v>
+      </c>
+      <c r="F30">
+        <v>9</v>
+      </c>
+      <c r="G30">
+        <v>10</v>
+      </c>
+      <c r="H30">
+        <v>8</v>
+      </c>
+      <c r="I30">
+        <v>8</v>
+      </c>
+      <c r="J30">
+        <v>9</v>
+      </c>
+      <c r="K30">
+        <v>9</v>
+      </c>
+      <c r="L30">
+        <v>8</v>
+      </c>
     </row>
     <row r="31" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B31">
@@ -965,7 +1119,31 @@
         <v>10</v>
       </c>
       <c r="D31">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="E31">
+        <v>8</v>
+      </c>
+      <c r="F31">
+        <v>8</v>
+      </c>
+      <c r="G31">
+        <v>5</v>
+      </c>
+      <c r="H31">
+        <v>8</v>
+      </c>
+      <c r="I31">
+        <v>8</v>
+      </c>
+      <c r="J31">
+        <v>8</v>
+      </c>
+      <c r="K31">
+        <v>8</v>
+      </c>
+      <c r="L31">
+        <v>7</v>
       </c>
     </row>
     <row r="32" spans="2:12" x14ac:dyDescent="0.2">
@@ -978,6 +1156,30 @@
       <c r="D32">
         <v>15</v>
       </c>
+      <c r="E32">
+        <v>15</v>
+      </c>
+      <c r="F32">
+        <v>13</v>
+      </c>
+      <c r="G32">
+        <v>11</v>
+      </c>
+      <c r="H32">
+        <v>7</v>
+      </c>
+      <c r="I32">
+        <v>12</v>
+      </c>
+      <c r="J32">
+        <v>13</v>
+      </c>
+      <c r="K32">
+        <v>15</v>
+      </c>
+      <c r="L32">
+        <v>11</v>
+      </c>
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B33">
@@ -989,6 +1191,30 @@
       <c r="D33">
         <v>9</v>
       </c>
+      <c r="E33">
+        <v>9</v>
+      </c>
+      <c r="F33">
+        <v>9</v>
+      </c>
+      <c r="G33">
+        <v>9</v>
+      </c>
+      <c r="H33">
+        <v>6</v>
+      </c>
+      <c r="I33">
+        <v>9</v>
+      </c>
+      <c r="J33">
+        <v>9</v>
+      </c>
+      <c r="K33">
+        <v>9</v>
+      </c>
+      <c r="L33">
+        <v>9</v>
+      </c>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B34">
@@ -1000,6 +1226,30 @@
       <c r="D34">
         <v>5</v>
       </c>
+      <c r="E34">
+        <v>4</v>
+      </c>
+      <c r="F34">
+        <v>5</v>
+      </c>
+      <c r="G34">
+        <v>5</v>
+      </c>
+      <c r="H34">
+        <v>5</v>
+      </c>
+      <c r="I34">
+        <v>5</v>
+      </c>
+      <c r="J34">
+        <v>5</v>
+      </c>
+      <c r="K34">
+        <v>5</v>
+      </c>
+      <c r="L34">
+        <v>4</v>
+      </c>
     </row>
     <row r="35" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B35">
@@ -1010,6 +1260,30 @@
       </c>
       <c r="D35">
         <v>6</v>
+      </c>
+      <c r="E35">
+        <v>8</v>
+      </c>
+      <c r="F35">
+        <v>4</v>
+      </c>
+      <c r="G35">
+        <v>5</v>
+      </c>
+      <c r="H35">
+        <v>4</v>
+      </c>
+      <c r="I35">
+        <v>7</v>
+      </c>
+      <c r="J35">
+        <v>6</v>
+      </c>
+      <c r="K35">
+        <v>8</v>
+      </c>
+      <c r="L35">
+        <v>5</v>
       </c>
     </row>
     <row r="36" spans="2:12" x14ac:dyDescent="0.2">
@@ -1022,39 +1296,39 @@
       </c>
       <c r="D36">
         <f t="shared" ref="D36:L36" si="5">SUM(D26:D35)</f>
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E36">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="F36">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="G36">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="H36">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="I36">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="J36">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="K36">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="L36">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>83</v>
       </c>
     </row>
   </sheetData>

--- a/Advanced Reactor Materials/Fall2025/grading.xlsx
+++ b/Advanced Reactor Materials/Fall2025/grading.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10913"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10928"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/beelbw/projects/TEACHING/Advanced Reactor Materials/Fall2025/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0806182-D537-BD45-8EF0-7653B7F6AC91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7971EC3-424C-9747-BF72-DD764A6A8D97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5120" yWindow="8740" windowWidth="24220" windowHeight="17440" xr2:uid="{4E6CEA4E-2509-754B-9890-44C713F10933}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="22">
   <si>
     <t>Roster</t>
   </si>
@@ -477,7 +477,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7A9E859-0099-8A4F-9892-6572C8559B21}">
-  <dimension ref="B2:N36"/>
+  <dimension ref="B2:N49"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="20.1640625" customWidth="1"/>
@@ -1331,6 +1331,166 @@
         <v>83</v>
       </c>
     </row>
+    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B38" t="s">
+        <v>11</v>
+      </c>
+      <c r="C38" t="s">
+        <v>18</v>
+      </c>
+      <c r="D38" t="s">
+        <v>1</v>
+      </c>
+      <c r="E38" t="s">
+        <v>2</v>
+      </c>
+      <c r="F38" t="s">
+        <v>20</v>
+      </c>
+      <c r="G38" t="s">
+        <v>5</v>
+      </c>
+      <c r="H38" t="s">
+        <v>6</v>
+      </c>
+      <c r="I38" t="s">
+        <v>8</v>
+      </c>
+      <c r="J38" t="s">
+        <v>9</v>
+      </c>
+      <c r="K38" t="s">
+        <v>4</v>
+      </c>
+      <c r="L38" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B39">
+        <v>1</v>
+      </c>
+      <c r="C39">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B40">
+        <v>2</v>
+      </c>
+      <c r="C40">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B41">
+        <v>3</v>
+      </c>
+      <c r="C41">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B42">
+        <v>4</v>
+      </c>
+      <c r="C42">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B43">
+        <v>5</v>
+      </c>
+      <c r="C43">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B44">
+        <v>6</v>
+      </c>
+      <c r="C44">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B45">
+        <v>7</v>
+      </c>
+      <c r="C45">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B46">
+        <v>8</v>
+      </c>
+      <c r="C46">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B47">
+        <v>9</v>
+      </c>
+      <c r="C47">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B48">
+        <v>10</v>
+      </c>
+      <c r="C48">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B49" t="s">
+        <v>21</v>
+      </c>
+      <c r="C49">
+        <f>SUM(C39:C48)</f>
+        <v>100</v>
+      </c>
+      <c r="D49">
+        <f t="shared" ref="D49:L49" si="6">SUM(D39:D48)</f>
+        <v>0</v>
+      </c>
+      <c r="E49">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F49">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="G49">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="H49">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="I49">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="K49">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="L49">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Advanced Reactor Materials/Fall2025/grading.xlsx
+++ b/Advanced Reactor Materials/Fall2025/grading.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/beelbw/projects/TEACHING/Advanced Reactor Materials/Fall2025/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7971EC3-424C-9747-BF72-DD764A6A8D97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D5E0DEA-8F99-4A49-9CB9-5B1771CAD486}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5120" yWindow="8740" windowWidth="24220" windowHeight="17440" xr2:uid="{4E6CEA4E-2509-754B-9890-44C713F10933}"/>
+    <workbookView xWindow="6140" yWindow="6760" windowWidth="24220" windowHeight="17440" xr2:uid="{4E6CEA4E-2509-754B-9890-44C713F10933}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="24">
   <si>
     <t>Roster</t>
   </si>
@@ -102,6 +102,12 @@
   </si>
   <si>
     <t>sum</t>
+  </si>
+  <si>
+    <t>Current</t>
+  </si>
+  <si>
+    <t>Stdev</t>
   </si>
 </sst>
 </file>
@@ -140,9 +146,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -477,7 +484,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7A9E859-0099-8A4F-9892-6572C8559B21}">
-  <dimension ref="B2:N49"/>
+  <dimension ref="B2:O50"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="20.1640625" customWidth="1"/>
@@ -485,12 +492,12 @@
     <col min="9" max="9" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C3">
         <v>0.2</v>
       </c>
@@ -507,12 +514,12 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="4" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:15" x14ac:dyDescent="0.2">
       <c r="I4" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B5" t="s">
         <v>0</v>
       </c>
@@ -549,298 +556,368 @@
       <c r="N5" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="6" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B6" t="s">
         <v>1</v>
       </c>
       <c r="C6">
         <v>95</v>
       </c>
+      <c r="D6">
+        <v>93</v>
+      </c>
       <c r="I6">
-        <f t="shared" ref="I6:M12" si="0">(C6+C$19)*C$3</f>
+        <f>(C6+C$20)*C$3</f>
         <v>19.400000000000002</v>
       </c>
       <c r="J6">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>(D6+D$20)*D$3</f>
+        <v>19.600000000000001</v>
       </c>
       <c r="K6">
-        <f t="shared" si="0"/>
+        <f>(E6+E$20)*E$3</f>
         <v>0</v>
       </c>
       <c r="L6">
-        <f t="shared" si="0"/>
+        <f>(F6+F$20)*F$3</f>
         <v>0</v>
       </c>
       <c r="M6">
-        <f t="shared" si="0"/>
+        <f>(G6+G$20)*G$3</f>
         <v>0</v>
       </c>
       <c r="N6">
         <f>SUM(I6:M6)</f>
-        <v>19.400000000000002</v>
-      </c>
-    </row>
-    <row r="7" spans="2:14" x14ac:dyDescent="0.2">
+        <v>39</v>
+      </c>
+      <c r="O6" s="2">
+        <f>N6/40</f>
+        <v>0.97499999999999998</v>
+      </c>
+    </row>
+    <row r="7" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B7" t="s">
         <v>2</v>
       </c>
       <c r="C7">
         <v>94</v>
       </c>
+      <c r="D7">
+        <v>91</v>
+      </c>
       <c r="I7">
-        <f t="shared" si="0"/>
+        <f>(C7+C$20)*C$3</f>
         <v>19.200000000000003</v>
       </c>
       <c r="J7">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>(D7+D$20)*D$3</f>
+        <v>19.200000000000003</v>
       </c>
       <c r="K7">
-        <f t="shared" si="0"/>
+        <f>(E7+E$20)*E$3</f>
         <v>0</v>
       </c>
       <c r="L7">
-        <f t="shared" si="0"/>
+        <f>(F7+F$20)*F$3</f>
         <v>0</v>
       </c>
       <c r="M7">
-        <f t="shared" si="0"/>
+        <f>(G7+G$20)*G$3</f>
         <v>0</v>
       </c>
       <c r="N7">
-        <f t="shared" ref="N7:N16" si="1">SUM(I7:M7)</f>
-        <v>19.200000000000003</v>
-      </c>
-    </row>
-    <row r="8" spans="2:14" x14ac:dyDescent="0.2">
+        <f t="shared" ref="N7:N16" si="0">SUM(I7:M7)</f>
+        <v>38.400000000000006</v>
+      </c>
+      <c r="O7" s="2">
+        <f t="shared" ref="O7:O16" si="1">N7/40</f>
+        <v>0.96000000000000019</v>
+      </c>
+    </row>
+    <row r="8" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B8" t="s">
         <v>20</v>
       </c>
       <c r="C8">
         <v>89</v>
       </c>
+      <c r="D8">
+        <v>93</v>
+      </c>
       <c r="I8">
-        <f t="shared" si="0"/>
+        <f>(C8+C$20)*C$3</f>
         <v>18.2</v>
       </c>
       <c r="J8">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>(D8+D$20)*D$3</f>
+        <v>19.600000000000001</v>
       </c>
       <c r="K8">
-        <f t="shared" si="0"/>
+        <f>(E8+E$20)*E$3</f>
         <v>0</v>
       </c>
       <c r="L8">
-        <f t="shared" si="0"/>
+        <f>(F8+F$20)*F$3</f>
         <v>0</v>
       </c>
       <c r="M8">
-        <f t="shared" si="0"/>
+        <f>(G8+G$20)*G$3</f>
         <v>0</v>
       </c>
       <c r="N8">
         <f t="shared" ref="N8" si="2">SUM(I8:M8)</f>
-        <v>18.2</v>
-      </c>
-    </row>
-    <row r="9" spans="2:14" x14ac:dyDescent="0.2">
+        <v>37.799999999999997</v>
+      </c>
+      <c r="O8" s="2">
+        <f t="shared" si="1"/>
+        <v>0.94499999999999995</v>
+      </c>
+    </row>
+    <row r="9" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B9" t="s">
         <v>5</v>
       </c>
       <c r="C9">
         <v>84</v>
       </c>
+      <c r="D9">
+        <v>68</v>
+      </c>
       <c r="I9">
+        <f>(C9+C$20)*C$3</f>
+        <v>17.2</v>
+      </c>
+      <c r="J9">
+        <f>(D9+D$20)*D$3</f>
+        <v>14.600000000000001</v>
+      </c>
+      <c r="K9">
+        <f>(E9+E$20)*E$3</f>
+        <v>0</v>
+      </c>
+      <c r="L9">
+        <f>(F9+F$20)*F$3</f>
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <f>(G9+G$20)*G$3</f>
+        <v>0</v>
+      </c>
+      <c r="N9">
         <f t="shared" si="0"/>
-        <v>17.2</v>
-      </c>
-      <c r="J9">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K9">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="L9">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="M9">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="N9">
+        <v>31.8</v>
+      </c>
+      <c r="O9" s="2">
         <f t="shared" si="1"/>
-        <v>17.2</v>
-      </c>
-    </row>
-    <row r="10" spans="2:14" x14ac:dyDescent="0.2">
+        <v>0.79500000000000004</v>
+      </c>
+    </row>
+    <row r="10" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B10" t="s">
         <v>6</v>
       </c>
       <c r="C10">
         <v>74</v>
       </c>
+      <c r="D10">
+        <v>73</v>
+      </c>
       <c r="I10">
+        <f>(C10+C$20)*C$3</f>
+        <v>15.200000000000001</v>
+      </c>
+      <c r="J10">
+        <f>(D10+D$20)*D$3</f>
+        <v>15.600000000000001</v>
+      </c>
+      <c r="K10">
+        <f>(E10+E$20)*E$3</f>
+        <v>0</v>
+      </c>
+      <c r="L10">
+        <f>(F10+F$20)*F$3</f>
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <f>(G10+G$20)*G$3</f>
+        <v>0</v>
+      </c>
+      <c r="N10">
         <f t="shared" si="0"/>
-        <v>15.200000000000001</v>
-      </c>
-      <c r="J10">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K10">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="L10">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="M10">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="N10">
+        <v>30.800000000000004</v>
+      </c>
+      <c r="O10" s="2">
         <f t="shared" si="1"/>
-        <v>15.200000000000001</v>
-      </c>
-    </row>
-    <row r="11" spans="2:14" x14ac:dyDescent="0.2">
+        <v>0.77000000000000013</v>
+      </c>
+    </row>
+    <row r="11" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B11" t="s">
         <v>8</v>
       </c>
       <c r="C11">
         <v>90</v>
       </c>
+      <c r="D11">
+        <v>88</v>
+      </c>
       <c r="I11">
+        <f>(C11+C$20)*C$3</f>
+        <v>18.400000000000002</v>
+      </c>
+      <c r="J11">
+        <f>(D11+D$20)*D$3</f>
+        <v>18.600000000000001</v>
+      </c>
+      <c r="K11">
+        <f>(E11+E$20)*E$3</f>
+        <v>0</v>
+      </c>
+      <c r="L11">
+        <f>(F11+F$20)*F$3</f>
+        <v>0</v>
+      </c>
+      <c r="M11">
+        <f>(G11+G$20)*G$3</f>
+        <v>0</v>
+      </c>
+      <c r="N11">
         <f t="shared" si="0"/>
-        <v>18.400000000000002</v>
-      </c>
-      <c r="J11">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K11">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="L11">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="M11">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="N11">
+        <v>37</v>
+      </c>
+      <c r="O11" s="2">
         <f t="shared" si="1"/>
-        <v>18.400000000000002</v>
-      </c>
-    </row>
-    <row r="12" spans="2:14" x14ac:dyDescent="0.2">
+        <v>0.92500000000000004</v>
+      </c>
+    </row>
+    <row r="12" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B12" t="s">
         <v>9</v>
       </c>
       <c r="C12">
         <v>91</v>
       </c>
+      <c r="D12">
+        <v>97</v>
+      </c>
       <c r="I12">
+        <f>(C12+C$20)*C$3</f>
+        <v>18.600000000000001</v>
+      </c>
+      <c r="J12">
+        <f>(D12+D$20)*D$3</f>
+        <v>20.400000000000002</v>
+      </c>
+      <c r="K12">
+        <f>(E12+E$20)*E$3</f>
+        <v>0</v>
+      </c>
+      <c r="L12">
+        <f>(F12+F$20)*F$3</f>
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <f>(G12+G$20)*G$3</f>
+        <v>0</v>
+      </c>
+      <c r="N12">
         <f t="shared" si="0"/>
-        <v>18.600000000000001</v>
-      </c>
-      <c r="J12">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K12">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="L12">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="M12">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="N12">
+        <v>39</v>
+      </c>
+      <c r="O12" s="2">
         <f t="shared" si="1"/>
-        <v>18.600000000000001</v>
-      </c>
-    </row>
-    <row r="14" spans="2:14" x14ac:dyDescent="0.2">
+        <v>0.97499999999999998</v>
+      </c>
+    </row>
+    <row r="13" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O13" s="2"/>
+    </row>
+    <row r="14" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B14" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O14" s="2"/>
+    </row>
+    <row r="15" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B15" t="s">
         <v>4</v>
       </c>
       <c r="C15">
         <v>97</v>
       </c>
+      <c r="D15">
+        <v>97</v>
+      </c>
       <c r="I15">
-        <f t="shared" ref="I15:M16" si="3">(C15+C$19)*C$3</f>
+        <f>(C15+C$20)*C$3</f>
         <v>19.8</v>
       </c>
       <c r="J15">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f>(D15+D$20)*D$3</f>
+        <v>20.400000000000002</v>
       </c>
       <c r="K15">
-        <f t="shared" si="3"/>
+        <f>(E15+E$20)*E$3</f>
         <v>0</v>
       </c>
       <c r="L15">
-        <f t="shared" si="3"/>
+        <f>(F15+F$20)*F$3</f>
         <v>0</v>
       </c>
       <c r="M15">
-        <f t="shared" si="3"/>
+        <f>(G15+G$20)*G$3</f>
         <v>0</v>
       </c>
       <c r="N15">
+        <f t="shared" si="0"/>
+        <v>40.200000000000003</v>
+      </c>
+      <c r="O15" s="2">
         <f t="shared" si="1"/>
-        <v>19.8</v>
-      </c>
-    </row>
-    <row r="16" spans="2:14" x14ac:dyDescent="0.2">
+        <v>1.0050000000000001</v>
+      </c>
+    </row>
+    <row r="16" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B16" t="s">
         <v>7</v>
       </c>
       <c r="C16">
         <v>83</v>
       </c>
+      <c r="D16">
+        <v>79</v>
+      </c>
       <c r="I16">
-        <f t="shared" si="3"/>
+        <f>(C16+C$20)*C$3</f>
         <v>17</v>
       </c>
       <c r="J16">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f>(D16+D$20)*D$3</f>
+        <v>16.8</v>
       </c>
       <c r="K16">
-        <f t="shared" si="3"/>
+        <f>(E16+E$20)*E$3</f>
         <v>0</v>
       </c>
       <c r="L16">
-        <f t="shared" si="3"/>
+        <f>(F16+F$20)*F$3</f>
         <v>0</v>
       </c>
       <c r="M16">
-        <f t="shared" si="3"/>
+        <f>(G16+G$20)*G$3</f>
         <v>0</v>
       </c>
       <c r="N16">
+        <f t="shared" si="0"/>
+        <v>33.799999999999997</v>
+      </c>
+      <c r="O16" s="2">
         <f t="shared" si="1"/>
-        <v>17</v>
+        <v>0.84499999999999997</v>
       </c>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.2">
@@ -851,9 +928,9 @@
         <f>AVERAGE(C6:C16)</f>
         <v>88.555555555555557</v>
       </c>
-      <c r="D18" s="1" t="e">
+      <c r="D18" s="1">
         <f>AVERAGE(D6:D16)</f>
-        <v>#DIV/0!</v>
+        <v>86.555555555555557</v>
       </c>
       <c r="E18" s="1" t="e">
         <f>AVERAGE(E6:E16)</f>
@@ -870,145 +947,129 @@
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B19" t="s">
-        <v>16</v>
-      </c>
-      <c r="C19">
-        <v>2</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="C19" s="1">
+        <f>STDEV(C6:C16)</f>
+        <v>7.195677714974301</v>
+      </c>
+      <c r="D19" s="1">
+        <f>STDEV(D6:D16)</f>
+        <v>10.654941472283054</v>
+      </c>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1"/>
     </row>
     <row r="20" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B20" t="s">
+        <v>16</v>
+      </c>
+      <c r="C20">
+        <v>2</v>
+      </c>
+      <c r="D20">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B21" t="s">
         <v>17</v>
       </c>
-      <c r="C20" s="1">
-        <f>C18+C19</f>
+      <c r="C21" s="1">
+        <f>C18+C20</f>
         <v>90.555555555555557</v>
       </c>
-      <c r="D20" s="1" t="e">
-        <f t="shared" ref="D20:G20" si="4">D18+D19</f>
+      <c r="D21" s="1">
+        <f>D18+D20</f>
+        <v>91.555555555555557</v>
+      </c>
+      <c r="E21" s="1" t="e">
+        <f t="shared" ref="D21:G21" si="3">E18+E20</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E20" s="1" t="e">
-        <f t="shared" si="4"/>
+      <c r="F21" s="1" t="e">
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F20" s="1" t="e">
-        <f t="shared" si="4"/>
+      <c r="G21" s="1" t="e">
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="G20" s="1" t="e">
-        <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="25" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B25" t="s">
-        <v>10</v>
-      </c>
-      <c r="C25" t="s">
+    </row>
+    <row r="26" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B26" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" t="s">
         <v>18</v>
       </c>
-      <c r="D25" t="s">
+      <c r="D26" t="s">
         <v>1</v>
       </c>
-      <c r="E25" t="s">
+      <c r="E26" t="s">
         <v>2</v>
       </c>
-      <c r="F25" t="s">
+      <c r="F26" t="s">
         <v>20</v>
       </c>
-      <c r="G25" t="s">
-        <v>5</v>
-      </c>
-      <c r="H25" t="s">
-        <v>6</v>
-      </c>
-      <c r="I25" t="s">
-        <v>8</v>
-      </c>
-      <c r="J25" t="s">
-        <v>9</v>
-      </c>
-      <c r="K25" t="s">
+      <c r="G26" t="s">
+        <v>5</v>
+      </c>
+      <c r="H26" t="s">
+        <v>6</v>
+      </c>
+      <c r="I26" t="s">
+        <v>8</v>
+      </c>
+      <c r="J26" t="s">
+        <v>9</v>
+      </c>
+      <c r="K26" t="s">
         <v>4</v>
       </c>
-      <c r="L25" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="26" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B26">
-        <v>1</v>
-      </c>
-      <c r="C26">
-        <v>8</v>
-      </c>
-      <c r="D26">
-        <v>7</v>
-      </c>
-      <c r="E26">
-        <v>8</v>
-      </c>
-      <c r="F26">
-        <v>7</v>
-      </c>
-      <c r="G26">
-        <v>7</v>
-      </c>
-      <c r="H26">
-        <v>7</v>
-      </c>
-      <c r="I26">
-        <v>8</v>
-      </c>
-      <c r="J26">
-        <v>8</v>
-      </c>
-      <c r="K26">
-        <v>8</v>
-      </c>
-      <c r="L26">
-        <v>8</v>
+      <c r="L26" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C27">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D27">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E27">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F27">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G27">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H27">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I27">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J27">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K27">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L27">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B28">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C28">
         <v>10</v>
@@ -1026,94 +1087,94 @@
         <v>10</v>
       </c>
       <c r="H28">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I28">
         <v>10</v>
       </c>
       <c r="J28">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K28">
         <v>10</v>
       </c>
       <c r="L28">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="29" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B29">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C29">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D29">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E29">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F29">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G29">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H29">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="I29">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J29">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="K29">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="L29">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="30" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B30">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C30">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D30">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E30">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F30">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="G30">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H30">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I30">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="J30">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="K30">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="L30">
-        <v>8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="31" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B31">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C31">
         <v>10</v>
@@ -1125,10 +1186,10 @@
         <v>8</v>
       </c>
       <c r="F31">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G31">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H31">
         <v>8</v>
@@ -1137,358 +1198,663 @@
         <v>8</v>
       </c>
       <c r="J31">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K31">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L31">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="32" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B32">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C32">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D32">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E32">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F32">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="G32">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="H32">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I32">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J32">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="K32">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="L32">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B33">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C33">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D33">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E33">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="F33">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G33">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H33">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I33">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="J33">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="K33">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="L33">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B34">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C34">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D34">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E34">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F34">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G34">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H34">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I34">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="J34">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="K34">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L34">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="35" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B35">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C35">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D35">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E35">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F35">
+        <v>5</v>
+      </c>
+      <c r="G35">
+        <v>5</v>
+      </c>
+      <c r="H35">
+        <v>5</v>
+      </c>
+      <c r="I35">
+        <v>5</v>
+      </c>
+      <c r="J35">
+        <v>5</v>
+      </c>
+      <c r="K35">
+        <v>5</v>
+      </c>
+      <c r="L35">
         <v>4</v>
       </c>
-      <c r="G35">
-        <v>5</v>
-      </c>
-      <c r="H35">
+    </row>
+    <row r="36" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B36">
+        <v>10</v>
+      </c>
+      <c r="C36">
+        <v>8</v>
+      </c>
+      <c r="D36">
+        <v>6</v>
+      </c>
+      <c r="E36">
+        <v>8</v>
+      </c>
+      <c r="F36">
         <v>4</v>
       </c>
-      <c r="I35">
-        <v>7</v>
-      </c>
-      <c r="J35">
-        <v>6</v>
-      </c>
-      <c r="K35">
-        <v>8</v>
-      </c>
-      <c r="L35">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="36" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B36" t="s">
+      <c r="G36">
+        <v>5</v>
+      </c>
+      <c r="H36">
+        <v>4</v>
+      </c>
+      <c r="I36">
+        <v>7</v>
+      </c>
+      <c r="J36">
+        <v>6</v>
+      </c>
+      <c r="K36">
+        <v>8</v>
+      </c>
+      <c r="L36">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B37" t="s">
         <v>21</v>
       </c>
-      <c r="C36">
-        <f>SUM(C26:C35)</f>
+      <c r="C37">
+        <f>SUM(C27:C36)</f>
         <v>100</v>
       </c>
-      <c r="D36">
-        <f t="shared" ref="D36:L36" si="5">SUM(D26:D35)</f>
+      <c r="D37">
+        <f t="shared" ref="D37:L37" si="4">SUM(D27:D36)</f>
         <v>95</v>
       </c>
-      <c r="E36">
-        <f t="shared" si="5"/>
+      <c r="E37">
+        <f t="shared" si="4"/>
         <v>94</v>
       </c>
-      <c r="F36">
-        <f t="shared" si="5"/>
+      <c r="F37">
+        <f t="shared" si="4"/>
         <v>89</v>
       </c>
-      <c r="G36">
-        <f t="shared" si="5"/>
+      <c r="G37">
+        <f t="shared" si="4"/>
         <v>84</v>
       </c>
-      <c r="H36">
-        <f t="shared" si="5"/>
+      <c r="H37">
+        <f t="shared" si="4"/>
         <v>74</v>
       </c>
-      <c r="I36">
-        <f t="shared" si="5"/>
+      <c r="I37">
+        <f t="shared" si="4"/>
         <v>90</v>
       </c>
-      <c r="J36">
+      <c r="J37">
+        <f t="shared" si="4"/>
+        <v>91</v>
+      </c>
+      <c r="K37">
+        <f t="shared" si="4"/>
+        <v>97</v>
+      </c>
+      <c r="L37">
+        <f t="shared" si="4"/>
+        <v>83</v>
+      </c>
+    </row>
+    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B39" t="s">
+        <v>11</v>
+      </c>
+      <c r="C39" t="s">
+        <v>18</v>
+      </c>
+      <c r="D39" t="s">
+        <v>1</v>
+      </c>
+      <c r="E39" t="s">
+        <v>2</v>
+      </c>
+      <c r="F39" t="s">
+        <v>20</v>
+      </c>
+      <c r="G39" t="s">
+        <v>5</v>
+      </c>
+      <c r="H39" t="s">
+        <v>6</v>
+      </c>
+      <c r="I39" t="s">
+        <v>8</v>
+      </c>
+      <c r="J39" t="s">
+        <v>9</v>
+      </c>
+      <c r="K39" t="s">
+        <v>4</v>
+      </c>
+      <c r="L39" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B40">
+        <v>1</v>
+      </c>
+      <c r="C40">
+        <v>6</v>
+      </c>
+      <c r="D40">
+        <v>5</v>
+      </c>
+      <c r="E40">
+        <v>6</v>
+      </c>
+      <c r="F40">
+        <v>6</v>
+      </c>
+      <c r="G40">
+        <v>4</v>
+      </c>
+      <c r="H40">
+        <v>4</v>
+      </c>
+      <c r="I40">
+        <v>5</v>
+      </c>
+      <c r="J40">
+        <v>6</v>
+      </c>
+      <c r="K40">
+        <v>5</v>
+      </c>
+      <c r="L40">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B41">
+        <v>2</v>
+      </c>
+      <c r="C41">
+        <v>6</v>
+      </c>
+      <c r="D41">
+        <v>6</v>
+      </c>
+      <c r="E41">
+        <v>6</v>
+      </c>
+      <c r="F41">
+        <v>5</v>
+      </c>
+      <c r="G41">
+        <v>6</v>
+      </c>
+      <c r="H41">
+        <v>6</v>
+      </c>
+      <c r="I41">
+        <v>5</v>
+      </c>
+      <c r="J41">
+        <v>6</v>
+      </c>
+      <c r="K41">
+        <v>6</v>
+      </c>
+      <c r="L41">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B42">
+        <v>3</v>
+      </c>
+      <c r="C42">
+        <v>10</v>
+      </c>
+      <c r="D42">
+        <v>10</v>
+      </c>
+      <c r="E42">
+        <v>10</v>
+      </c>
+      <c r="F42">
+        <v>10</v>
+      </c>
+      <c r="G42">
+        <v>9</v>
+      </c>
+      <c r="H42">
+        <v>9</v>
+      </c>
+      <c r="I42">
+        <v>10</v>
+      </c>
+      <c r="J42">
+        <v>10</v>
+      </c>
+      <c r="K42">
+        <v>10</v>
+      </c>
+      <c r="L42">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B43">
+        <v>4</v>
+      </c>
+      <c r="C43">
+        <v>12</v>
+      </c>
+      <c r="D43">
+        <v>10</v>
+      </c>
+      <c r="E43">
+        <v>11</v>
+      </c>
+      <c r="F43">
+        <v>10</v>
+      </c>
+      <c r="G43">
+        <v>7</v>
+      </c>
+      <c r="H43">
+        <v>5</v>
+      </c>
+      <c r="I43">
+        <v>8</v>
+      </c>
+      <c r="J43">
+        <v>11</v>
+      </c>
+      <c r="K43">
+        <v>12</v>
+      </c>
+      <c r="L43">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B44">
+        <v>5</v>
+      </c>
+      <c r="C44">
+        <v>8</v>
+      </c>
+      <c r="D44">
+        <v>8</v>
+      </c>
+      <c r="E44">
+        <v>8</v>
+      </c>
+      <c r="F44">
+        <v>8</v>
+      </c>
+      <c r="G44">
+        <v>7</v>
+      </c>
+      <c r="H44">
+        <v>5</v>
+      </c>
+      <c r="I44">
+        <v>7</v>
+      </c>
+      <c r="J44">
+        <v>8</v>
+      </c>
+      <c r="K44">
+        <v>8</v>
+      </c>
+      <c r="L44">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B45">
+        <v>6</v>
+      </c>
+      <c r="C45">
+        <v>15</v>
+      </c>
+      <c r="D45">
+        <v>15</v>
+      </c>
+      <c r="E45">
+        <v>14</v>
+      </c>
+      <c r="F45">
+        <v>13</v>
+      </c>
+      <c r="G45">
+        <v>5</v>
+      </c>
+      <c r="H45">
+        <v>14</v>
+      </c>
+      <c r="I45">
+        <v>13</v>
+      </c>
+      <c r="J45">
+        <v>14</v>
+      </c>
+      <c r="K45">
+        <v>14</v>
+      </c>
+      <c r="L45">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B46">
+        <v>7</v>
+      </c>
+      <c r="C46">
+        <v>15</v>
+      </c>
+      <c r="D46">
+        <v>14</v>
+      </c>
+      <c r="E46">
+        <v>13</v>
+      </c>
+      <c r="F46">
+        <v>15</v>
+      </c>
+      <c r="G46">
+        <v>14</v>
+      </c>
+      <c r="H46">
+        <v>12</v>
+      </c>
+      <c r="I46">
+        <v>14</v>
+      </c>
+      <c r="J46">
+        <v>15</v>
+      </c>
+      <c r="K46">
+        <v>14</v>
+      </c>
+      <c r="L46">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B47">
+        <v>8</v>
+      </c>
+      <c r="C47">
+        <v>8</v>
+      </c>
+      <c r="D47">
+        <v>6</v>
+      </c>
+      <c r="E47">
+        <v>5</v>
+      </c>
+      <c r="F47">
+        <v>7</v>
+      </c>
+      <c r="G47">
+        <v>1</v>
+      </c>
+      <c r="H47">
+        <v>3</v>
+      </c>
+      <c r="I47">
+        <v>6</v>
+      </c>
+      <c r="J47">
+        <v>8</v>
+      </c>
+      <c r="K47">
+        <v>8</v>
+      </c>
+      <c r="L47">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B48">
+        <v>9</v>
+      </c>
+      <c r="C48">
+        <v>12</v>
+      </c>
+      <c r="D48">
+        <v>11</v>
+      </c>
+      <c r="E48">
+        <v>11</v>
+      </c>
+      <c r="F48">
+        <v>11</v>
+      </c>
+      <c r="G48">
+        <v>9</v>
+      </c>
+      <c r="H48">
+        <v>8</v>
+      </c>
+      <c r="I48">
+        <v>12</v>
+      </c>
+      <c r="J48">
+        <v>12</v>
+      </c>
+      <c r="K48">
+        <v>12</v>
+      </c>
+      <c r="L48">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="49" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B49">
+        <v>10</v>
+      </c>
+      <c r="C49">
+        <v>8</v>
+      </c>
+      <c r="D49">
+        <v>8</v>
+      </c>
+      <c r="E49">
+        <v>7</v>
+      </c>
+      <c r="F49">
+        <v>8</v>
+      </c>
+      <c r="G49">
+        <v>6</v>
+      </c>
+      <c r="H49">
+        <v>7</v>
+      </c>
+      <c r="I49">
+        <v>8</v>
+      </c>
+      <c r="J49">
+        <v>7</v>
+      </c>
+      <c r="K49">
+        <v>8</v>
+      </c>
+      <c r="L49">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B50" t="s">
+        <v>21</v>
+      </c>
+      <c r="C50">
+        <f>SUM(C40:C49)</f>
+        <v>100</v>
+      </c>
+      <c r="D50">
+        <f t="shared" ref="D50:L50" si="5">SUM(D40:D49)</f>
+        <v>93</v>
+      </c>
+      <c r="E50">
         <f t="shared" si="5"/>
         <v>91</v>
       </c>
-      <c r="K36">
+      <c r="F50">
+        <f t="shared" si="5"/>
+        <v>93</v>
+      </c>
+      <c r="G50">
+        <f t="shared" si="5"/>
+        <v>68</v>
+      </c>
+      <c r="H50">
+        <f t="shared" si="5"/>
+        <v>73</v>
+      </c>
+      <c r="I50">
+        <f t="shared" si="5"/>
+        <v>88</v>
+      </c>
+      <c r="J50">
         <f t="shared" si="5"/>
         <v>97</v>
       </c>
-      <c r="L36">
+      <c r="K50">
         <f t="shared" si="5"/>
-        <v>83</v>
-      </c>
-    </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B38" t="s">
-        <v>11</v>
-      </c>
-      <c r="C38" t="s">
-        <v>18</v>
-      </c>
-      <c r="D38" t="s">
-        <v>1</v>
-      </c>
-      <c r="E38" t="s">
-        <v>2</v>
-      </c>
-      <c r="F38" t="s">
-        <v>20</v>
-      </c>
-      <c r="G38" t="s">
-        <v>5</v>
-      </c>
-      <c r="H38" t="s">
-        <v>6</v>
-      </c>
-      <c r="I38" t="s">
-        <v>8</v>
-      </c>
-      <c r="J38" t="s">
-        <v>9</v>
-      </c>
-      <c r="K38" t="s">
-        <v>4</v>
-      </c>
-      <c r="L38" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B39">
-        <v>1</v>
-      </c>
-      <c r="C39">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B40">
-        <v>2</v>
-      </c>
-      <c r="C40">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B41">
-        <v>3</v>
-      </c>
-      <c r="C41">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B42">
-        <v>4</v>
-      </c>
-      <c r="C42">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B43">
-        <v>5</v>
-      </c>
-      <c r="C43">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B44">
-        <v>6</v>
-      </c>
-      <c r="C44">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B45">
-        <v>7</v>
-      </c>
-      <c r="C45">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B46">
-        <v>8</v>
-      </c>
-      <c r="C46">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B47">
-        <v>9</v>
-      </c>
-      <c r="C47">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B48">
-        <v>10</v>
-      </c>
-      <c r="C48">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="49" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B49" t="s">
-        <v>21</v>
-      </c>
-      <c r="C49">
-        <f>SUM(C39:C48)</f>
-        <v>100</v>
-      </c>
-      <c r="D49">
-        <f t="shared" ref="D49:L49" si="6">SUM(D39:D48)</f>
-        <v>0</v>
-      </c>
-      <c r="E49">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F49">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="G49">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="H49">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="I49">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="J49">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="K49">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="L49">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <v>97</v>
+      </c>
+      <c r="L50">
+        <f t="shared" si="5"/>
+        <v>79</v>
       </c>
     </row>
   </sheetData>

--- a/Advanced Reactor Materials/Fall2025/grading.xlsx
+++ b/Advanced Reactor Materials/Fall2025/grading.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/beelbw/projects/TEACHING/Advanced Reactor Materials/Fall2025/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D5E0DEA-8F99-4A49-9CB9-5B1771CAD486}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5516EAE9-7263-2349-BBD9-C4EF6DC7D0E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6140" yWindow="6760" windowWidth="24220" windowHeight="17440" xr2:uid="{4E6CEA4E-2509-754B-9890-44C713F10933}"/>
+    <workbookView xWindow="3100" yWindow="4220" windowWidth="24220" windowHeight="17440" xr2:uid="{4E6CEA4E-2509-754B-9890-44C713F10933}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -570,33 +570,36 @@
       <c r="D6">
         <v>93</v>
       </c>
+      <c r="G6">
+        <v>100</v>
+      </c>
       <c r="I6">
-        <f>(C6+C$20)*C$3</f>
+        <f t="shared" ref="I6:M12" si="0">(C6+C$20)*C$3</f>
         <v>19.400000000000002</v>
       </c>
       <c r="J6">
-        <f>(D6+D$20)*D$3</f>
+        <f t="shared" si="0"/>
         <v>19.600000000000001</v>
       </c>
       <c r="K6">
-        <f>(E6+E$20)*E$3</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="L6">
-        <f>(F6+F$20)*F$3</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="M6">
-        <f>(G6+G$20)*G$3</f>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>20</v>
       </c>
       <c r="N6">
         <f>SUM(I6:M6)</f>
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="O6" s="2">
-        <f>N6/40</f>
-        <v>0.97499999999999998</v>
+        <f>N6/60</f>
+        <v>0.98333333333333328</v>
       </c>
     </row>
     <row r="7" spans="2:15" x14ac:dyDescent="0.2">
@@ -609,33 +612,36 @@
       <c r="D7">
         <v>91</v>
       </c>
+      <c r="G7">
+        <v>95</v>
+      </c>
       <c r="I7">
-        <f>(C7+C$20)*C$3</f>
+        <f t="shared" si="0"/>
         <v>19.200000000000003</v>
       </c>
       <c r="J7">
-        <f>(D7+D$20)*D$3</f>
+        <f t="shared" si="0"/>
         <v>19.200000000000003</v>
       </c>
       <c r="K7">
-        <f>(E7+E$20)*E$3</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="L7">
-        <f>(F7+F$20)*F$3</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="M7">
-        <f>(G7+G$20)*G$3</f>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>19</v>
       </c>
       <c r="N7">
-        <f t="shared" ref="N7:N16" si="0">SUM(I7:M7)</f>
-        <v>38.400000000000006</v>
+        <f t="shared" ref="N7:N16" si="1">SUM(I7:M7)</f>
+        <v>57.400000000000006</v>
       </c>
       <c r="O7" s="2">
-        <f t="shared" ref="O7:O16" si="1">N7/40</f>
-        <v>0.96000000000000019</v>
+        <f t="shared" ref="O7:O12" si="2">N7/60</f>
+        <v>0.95666666666666678</v>
       </c>
     </row>
     <row r="8" spans="2:15" x14ac:dyDescent="0.2">
@@ -648,33 +654,36 @@
       <c r="D8">
         <v>93</v>
       </c>
+      <c r="G8">
+        <v>96</v>
+      </c>
       <c r="I8">
-        <f>(C8+C$20)*C$3</f>
+        <f t="shared" si="0"/>
         <v>18.2</v>
       </c>
       <c r="J8">
-        <f>(D8+D$20)*D$3</f>
+        <f t="shared" si="0"/>
         <v>19.600000000000001</v>
       </c>
       <c r="K8">
-        <f>(E8+E$20)*E$3</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="L8">
-        <f>(F8+F$20)*F$3</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="M8">
-        <f>(G8+G$20)*G$3</f>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>19.200000000000003</v>
       </c>
       <c r="N8">
-        <f t="shared" ref="N8" si="2">SUM(I8:M8)</f>
-        <v>37.799999999999997</v>
+        <f t="shared" ref="N8" si="3">SUM(I8:M8)</f>
+        <v>57</v>
       </c>
       <c r="O8" s="2">
-        <f t="shared" si="1"/>
-        <v>0.94499999999999995</v>
+        <f t="shared" si="2"/>
+        <v>0.95</v>
       </c>
     </row>
     <row r="9" spans="2:15" x14ac:dyDescent="0.2">
@@ -687,33 +696,36 @@
       <c r="D9">
         <v>68</v>
       </c>
+      <c r="G9">
+        <v>96</v>
+      </c>
       <c r="I9">
-        <f>(C9+C$20)*C$3</f>
+        <f t="shared" si="0"/>
         <v>17.2</v>
       </c>
       <c r="J9">
-        <f>(D9+D$20)*D$3</f>
+        <f t="shared" si="0"/>
         <v>14.600000000000001</v>
       </c>
       <c r="K9">
-        <f>(E9+E$20)*E$3</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="L9">
-        <f>(F9+F$20)*F$3</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="M9">
-        <f>(G9+G$20)*G$3</f>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>19.200000000000003</v>
       </c>
       <c r="N9">
-        <f t="shared" si="0"/>
-        <v>31.8</v>
+        <f t="shared" si="1"/>
+        <v>51</v>
       </c>
       <c r="O9" s="2">
-        <f t="shared" si="1"/>
-        <v>0.79500000000000004</v>
+        <f t="shared" si="2"/>
+        <v>0.85</v>
       </c>
     </row>
     <row r="10" spans="2:15" x14ac:dyDescent="0.2">
@@ -726,33 +738,36 @@
       <c r="D10">
         <v>73</v>
       </c>
+      <c r="G10">
+        <v>93</v>
+      </c>
       <c r="I10">
-        <f>(C10+C$20)*C$3</f>
+        <f t="shared" si="0"/>
         <v>15.200000000000001</v>
       </c>
       <c r="J10">
-        <f>(D10+D$20)*D$3</f>
+        <f t="shared" si="0"/>
         <v>15.600000000000001</v>
       </c>
       <c r="K10">
-        <f>(E10+E$20)*E$3</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="L10">
-        <f>(F10+F$20)*F$3</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="M10">
-        <f>(G10+G$20)*G$3</f>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>18.600000000000001</v>
       </c>
       <c r="N10">
-        <f t="shared" si="0"/>
-        <v>30.800000000000004</v>
+        <f t="shared" si="1"/>
+        <v>49.400000000000006</v>
       </c>
       <c r="O10" s="2">
-        <f t="shared" si="1"/>
-        <v>0.77000000000000013</v>
+        <f t="shared" si="2"/>
+        <v>0.82333333333333347</v>
       </c>
     </row>
     <row r="11" spans="2:15" x14ac:dyDescent="0.2">
@@ -765,33 +780,36 @@
       <c r="D11">
         <v>88</v>
       </c>
+      <c r="G11">
+        <v>96</v>
+      </c>
       <c r="I11">
-        <f>(C11+C$20)*C$3</f>
+        <f t="shared" si="0"/>
         <v>18.400000000000002</v>
       </c>
       <c r="J11">
-        <f>(D11+D$20)*D$3</f>
+        <f t="shared" si="0"/>
         <v>18.600000000000001</v>
       </c>
       <c r="K11">
-        <f>(E11+E$20)*E$3</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="L11">
-        <f>(F11+F$20)*F$3</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="M11">
-        <f>(G11+G$20)*G$3</f>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>19.200000000000003</v>
       </c>
       <c r="N11">
-        <f t="shared" si="0"/>
-        <v>37</v>
+        <f t="shared" si="1"/>
+        <v>56.2</v>
       </c>
       <c r="O11" s="2">
-        <f t="shared" si="1"/>
-        <v>0.92500000000000004</v>
+        <f t="shared" si="2"/>
+        <v>0.93666666666666676</v>
       </c>
     </row>
     <row r="12" spans="2:15" x14ac:dyDescent="0.2">
@@ -804,33 +822,36 @@
       <c r="D12">
         <v>97</v>
       </c>
+      <c r="G12">
+        <v>98</v>
+      </c>
       <c r="I12">
-        <f>(C12+C$20)*C$3</f>
+        <f t="shared" si="0"/>
         <v>18.600000000000001</v>
       </c>
       <c r="J12">
-        <f>(D12+D$20)*D$3</f>
+        <f t="shared" si="0"/>
         <v>20.400000000000002</v>
       </c>
       <c r="K12">
-        <f>(E12+E$20)*E$3</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="L12">
-        <f>(F12+F$20)*F$3</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="M12">
-        <f>(G12+G$20)*G$3</f>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>19.600000000000001</v>
       </c>
       <c r="N12">
-        <f t="shared" si="0"/>
-        <v>39</v>
+        <f t="shared" si="1"/>
+        <v>58.6</v>
       </c>
       <c r="O12" s="2">
-        <f t="shared" si="1"/>
-        <v>0.97499999999999998</v>
+        <f t="shared" si="2"/>
+        <v>0.97666666666666668</v>
       </c>
     </row>
     <row r="13" spans="2:15" x14ac:dyDescent="0.2">
@@ -852,33 +873,36 @@
       <c r="D15">
         <v>97</v>
       </c>
+      <c r="G15">
+        <v>96</v>
+      </c>
       <c r="I15">
-        <f>(C15+C$20)*C$3</f>
+        <f t="shared" ref="I15:M16" si="4">(C15+C$20)*C$3</f>
         <v>19.8</v>
       </c>
       <c r="J15">
-        <f>(D15+D$20)*D$3</f>
+        <f t="shared" si="4"/>
         <v>20.400000000000002</v>
       </c>
       <c r="K15">
-        <f>(E15+E$20)*E$3</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="L15">
-        <f>(F15+F$20)*F$3</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M15">
-        <f>(G15+G$20)*G$3</f>
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>19.200000000000003</v>
       </c>
       <c r="N15">
-        <f t="shared" si="0"/>
-        <v>40.200000000000003</v>
+        <f t="shared" si="1"/>
+        <v>59.400000000000006</v>
       </c>
       <c r="O15" s="2">
-        <f t="shared" si="1"/>
-        <v>1.0050000000000001</v>
+        <f t="shared" ref="O15:O16" si="5">N15/60</f>
+        <v>0.9900000000000001</v>
       </c>
     </row>
     <row r="16" spans="2:15" x14ac:dyDescent="0.2">
@@ -891,33 +915,36 @@
       <c r="D16">
         <v>79</v>
       </c>
+      <c r="G16">
+        <v>96</v>
+      </c>
       <c r="I16">
-        <f>(C16+C$20)*C$3</f>
+        <f t="shared" si="4"/>
         <v>17</v>
       </c>
       <c r="J16">
-        <f>(D16+D$20)*D$3</f>
+        <f t="shared" si="4"/>
         <v>16.8</v>
       </c>
       <c r="K16">
-        <f>(E16+E$20)*E$3</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="L16">
-        <f>(F16+F$20)*F$3</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M16">
-        <f>(G16+G$20)*G$3</f>
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>19.200000000000003</v>
       </c>
       <c r="N16">
-        <f t="shared" si="0"/>
-        <v>33.799999999999997</v>
+        <f t="shared" si="1"/>
+        <v>53</v>
       </c>
       <c r="O16" s="2">
-        <f t="shared" si="1"/>
-        <v>0.84499999999999997</v>
+        <f t="shared" si="5"/>
+        <v>0.8833333333333333</v>
       </c>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.2">
@@ -940,9 +967,9 @@
         <f>AVERAGE(F6:F16)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G18" s="1" t="e">
+      <c r="G18" s="1">
         <f>AVERAGE(G6:G16)</f>
-        <v>#DIV/0!</v>
+        <v>96.222222222222229</v>
       </c>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.2">
@@ -985,16 +1012,16 @@
         <v>91.555555555555557</v>
       </c>
       <c r="E21" s="1" t="e">
-        <f t="shared" ref="D21:G21" si="3">E18+E20</f>
+        <f t="shared" ref="E21:G21" si="6">E18+E20</f>
         <v>#DIV/0!</v>
       </c>
       <c r="F21" s="1" t="e">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="G21" s="1" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
+      <c r="G21" s="1">
+        <f t="shared" si="6"/>
+        <v>96.222222222222229</v>
       </c>
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.2">
@@ -1391,39 +1418,39 @@
         <v>100</v>
       </c>
       <c r="D37">
-        <f t="shared" ref="D37:L37" si="4">SUM(D27:D36)</f>
+        <f t="shared" ref="D37:L37" si="7">SUM(D27:D36)</f>
         <v>95</v>
       </c>
       <c r="E37">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>94</v>
       </c>
       <c r="F37">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>89</v>
       </c>
       <c r="G37">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>84</v>
       </c>
       <c r="H37">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>74</v>
       </c>
       <c r="I37">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>90</v>
       </c>
       <c r="J37">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>91</v>
       </c>
       <c r="K37">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>97</v>
       </c>
       <c r="L37">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>83</v>
       </c>
     </row>
@@ -1821,39 +1848,39 @@
         <v>100</v>
       </c>
       <c r="D50">
-        <f t="shared" ref="D50:L50" si="5">SUM(D40:D49)</f>
+        <f t="shared" ref="D50:L50" si="8">SUM(D40:D49)</f>
         <v>93</v>
       </c>
       <c r="E50">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>91</v>
       </c>
       <c r="F50">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>93</v>
       </c>
       <c r="G50">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>68</v>
       </c>
       <c r="H50">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>73</v>
       </c>
       <c r="I50">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>88</v>
       </c>
       <c r="J50">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>97</v>
       </c>
       <c r="K50">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>97</v>
       </c>
       <c r="L50">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>79</v>
       </c>
     </row>

--- a/Advanced Reactor Materials/Fall2025/grading.xlsx
+++ b/Advanced Reactor Materials/Fall2025/grading.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/beelbw/projects/TEACHING/Advanced Reactor Materials/Fall2025/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5516EAE9-7263-2349-BBD9-C4EF6DC7D0E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B06010AA-0853-ED41-878C-1425292ADB20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3100" yWindow="4220" windowWidth="24220" windowHeight="17440" xr2:uid="{4E6CEA4E-2509-754B-9890-44C713F10933}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="24">
   <si>
     <t>Roster</t>
   </si>
@@ -484,7 +484,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7A9E859-0099-8A4F-9892-6572C8559B21}">
-  <dimension ref="B2:O50"/>
+  <dimension ref="B2:O65"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="20.1640625" customWidth="1"/>
@@ -1884,6 +1884,182 @@
         <v>79</v>
       </c>
     </row>
+    <row r="52" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B52" t="s">
+        <v>11</v>
+      </c>
+      <c r="C52" t="s">
+        <v>18</v>
+      </c>
+      <c r="D52" t="s">
+        <v>1</v>
+      </c>
+      <c r="E52" t="s">
+        <v>2</v>
+      </c>
+      <c r="F52" t="s">
+        <v>20</v>
+      </c>
+      <c r="G52" t="s">
+        <v>5</v>
+      </c>
+      <c r="H52" t="s">
+        <v>6</v>
+      </c>
+      <c r="I52" t="s">
+        <v>8</v>
+      </c>
+      <c r="J52" t="s">
+        <v>9</v>
+      </c>
+      <c r="K52" t="s">
+        <v>4</v>
+      </c>
+      <c r="L52" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="53" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B53">
+        <v>1</v>
+      </c>
+      <c r="C53">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="54" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B54">
+        <v>2</v>
+      </c>
+      <c r="C54">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="55" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B55">
+        <v>3</v>
+      </c>
+      <c r="C55">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="56" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B56">
+        <v>4</v>
+      </c>
+      <c r="C56">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="57" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B57">
+        <v>5</v>
+      </c>
+      <c r="C57">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="58" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B58">
+        <v>6</v>
+      </c>
+      <c r="C58">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="59" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B59">
+        <v>7</v>
+      </c>
+      <c r="C59">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="60" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B60">
+        <v>8</v>
+      </c>
+      <c r="C60">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B61">
+        <v>9</v>
+      </c>
+      <c r="C61">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="62" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B62">
+        <v>10</v>
+      </c>
+      <c r="C62">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="63" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B63">
+        <v>11</v>
+      </c>
+      <c r="C63">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="64" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B64">
+        <v>12</v>
+      </c>
+      <c r="C64">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B65" t="s">
+        <v>21</v>
+      </c>
+      <c r="C65">
+        <f>SUM(C53:C64)</f>
+        <v>100</v>
+      </c>
+      <c r="D65">
+        <f t="shared" ref="D65:L65" si="9">SUM(D53:D64)</f>
+        <v>0</v>
+      </c>
+      <c r="E65">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F65">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="G65">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="H65">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="I65">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="K65">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="L65">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Advanced Reactor Materials/Fall2025/grading.xlsx
+++ b/Advanced Reactor Materials/Fall2025/grading.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11102"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/beelbw/projects/TEACHING/Advanced Reactor Materials/Fall2025/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B06010AA-0853-ED41-878C-1425292ADB20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1A5EEDB-2619-F14C-88F2-787B94D06C47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3100" yWindow="4220" windowWidth="24220" windowHeight="17440" xr2:uid="{4E6CEA4E-2509-754B-9890-44C713F10933}"/>
+    <workbookView xWindow="3100" yWindow="4200" windowWidth="24220" windowHeight="17440" xr2:uid="{4E6CEA4E-2509-754B-9890-44C713F10933}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="26">
   <si>
     <t>Roster</t>
   </si>
@@ -108,6 +108,12 @@
   </si>
   <si>
     <t>Stdev</t>
+  </si>
+  <si>
+    <t>avg</t>
+  </si>
+  <si>
+    <t>stdev</t>
   </si>
 </sst>
 </file>
@@ -570,6 +576,9 @@
       <c r="D6">
         <v>93</v>
       </c>
+      <c r="E6">
+        <v>95</v>
+      </c>
       <c r="G6">
         <v>100</v>
       </c>
@@ -582,8 +591,8 @@
         <v>19.600000000000001</v>
       </c>
       <c r="K6">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>(E6+E$20)*E$3</f>
+        <v>20</v>
       </c>
       <c r="L6">
         <f t="shared" si="0"/>
@@ -595,11 +604,11 @@
       </c>
       <c r="N6">
         <f>SUM(I6:M6)</f>
-        <v>59</v>
+        <v>79</v>
       </c>
       <c r="O6" s="2">
-        <f>N6/60</f>
-        <v>0.98333333333333328</v>
+        <f>N6/80</f>
+        <v>0.98750000000000004</v>
       </c>
     </row>
     <row r="7" spans="2:15" x14ac:dyDescent="0.2">
@@ -612,6 +621,9 @@
       <c r="D7">
         <v>91</v>
       </c>
+      <c r="E7">
+        <v>89</v>
+      </c>
       <c r="G7">
         <v>95</v>
       </c>
@@ -625,7 +637,7 @@
       </c>
       <c r="K7">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>18.8</v>
       </c>
       <c r="L7">
         <f t="shared" si="0"/>
@@ -637,11 +649,11 @@
       </c>
       <c r="N7">
         <f t="shared" ref="N7:N16" si="1">SUM(I7:M7)</f>
-        <v>57.400000000000006</v>
+        <v>76.2</v>
       </c>
       <c r="O7" s="2">
-        <f t="shared" ref="O7:O12" si="2">N7/60</f>
-        <v>0.95666666666666678</v>
+        <f t="shared" ref="O7:O12" si="2">N7/80</f>
+        <v>0.95250000000000001</v>
       </c>
     </row>
     <row r="8" spans="2:15" x14ac:dyDescent="0.2">
@@ -654,6 +666,9 @@
       <c r="D8">
         <v>93</v>
       </c>
+      <c r="E8">
+        <v>90</v>
+      </c>
       <c r="G8">
         <v>96</v>
       </c>
@@ -667,7 +682,7 @@
       </c>
       <c r="K8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="L8">
         <f t="shared" si="0"/>
@@ -679,7 +694,7 @@
       </c>
       <c r="N8">
         <f t="shared" ref="N8" si="3">SUM(I8:M8)</f>
-        <v>57</v>
+        <v>76</v>
       </c>
       <c r="O8" s="2">
         <f t="shared" si="2"/>
@@ -696,6 +711,9 @@
       <c r="D9">
         <v>68</v>
       </c>
+      <c r="E9">
+        <v>83</v>
+      </c>
       <c r="G9">
         <v>96</v>
       </c>
@@ -709,7 +727,7 @@
       </c>
       <c r="K9">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>17.600000000000001</v>
       </c>
       <c r="L9">
         <f t="shared" si="0"/>
@@ -721,11 +739,11 @@
       </c>
       <c r="N9">
         <f t="shared" si="1"/>
-        <v>51</v>
+        <v>68.600000000000009</v>
       </c>
       <c r="O9" s="2">
         <f t="shared" si="2"/>
-        <v>0.85</v>
+        <v>0.85750000000000015</v>
       </c>
     </row>
     <row r="10" spans="2:15" x14ac:dyDescent="0.2">
@@ -738,6 +756,9 @@
       <c r="D10">
         <v>73</v>
       </c>
+      <c r="E10">
+        <v>77</v>
+      </c>
       <c r="G10">
         <v>93</v>
       </c>
@@ -751,7 +772,7 @@
       </c>
       <c r="K10">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>16.400000000000002</v>
       </c>
       <c r="L10">
         <f t="shared" si="0"/>
@@ -763,11 +784,11 @@
       </c>
       <c r="N10">
         <f t="shared" si="1"/>
-        <v>49.400000000000006</v>
+        <v>65.800000000000011</v>
       </c>
       <c r="O10" s="2">
         <f t="shared" si="2"/>
-        <v>0.82333333333333347</v>
+        <v>0.82250000000000012</v>
       </c>
     </row>
     <row r="11" spans="2:15" x14ac:dyDescent="0.2">
@@ -780,6 +801,9 @@
       <c r="D11">
         <v>88</v>
       </c>
+      <c r="E11">
+        <v>83</v>
+      </c>
       <c r="G11">
         <v>96</v>
       </c>
@@ -793,7 +817,7 @@
       </c>
       <c r="K11">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>17.600000000000001</v>
       </c>
       <c r="L11">
         <f t="shared" si="0"/>
@@ -805,11 +829,11 @@
       </c>
       <c r="N11">
         <f t="shared" si="1"/>
-        <v>56.2</v>
+        <v>73.800000000000011</v>
       </c>
       <c r="O11" s="2">
         <f t="shared" si="2"/>
-        <v>0.93666666666666676</v>
+        <v>0.9225000000000001</v>
       </c>
     </row>
     <row r="12" spans="2:15" x14ac:dyDescent="0.2">
@@ -822,6 +846,9 @@
       <c r="D12">
         <v>97</v>
       </c>
+      <c r="E12">
+        <v>84</v>
+      </c>
       <c r="G12">
         <v>98</v>
       </c>
@@ -835,7 +862,7 @@
       </c>
       <c r="K12">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>17.8</v>
       </c>
       <c r="L12">
         <f t="shared" si="0"/>
@@ -847,11 +874,11 @@
       </c>
       <c r="N12">
         <f t="shared" si="1"/>
-        <v>58.6</v>
+        <v>76.400000000000006</v>
       </c>
       <c r="O12" s="2">
         <f t="shared" si="2"/>
-        <v>0.97666666666666668</v>
+        <v>0.95500000000000007</v>
       </c>
     </row>
     <row r="13" spans="2:15" x14ac:dyDescent="0.2">
@@ -873,6 +900,9 @@
       <c r="D15">
         <v>97</v>
       </c>
+      <c r="E15">
+        <v>94</v>
+      </c>
       <c r="G15">
         <v>96</v>
       </c>
@@ -886,7 +916,7 @@
       </c>
       <c r="K15">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>19.8</v>
       </c>
       <c r="L15">
         <f t="shared" si="4"/>
@@ -897,12 +927,12 @@
         <v>19.200000000000003</v>
       </c>
       <c r="N15">
-        <f t="shared" si="1"/>
-        <v>59.400000000000006</v>
+        <f>SUM(I15:M15)</f>
+        <v>79.2</v>
       </c>
       <c r="O15" s="2">
-        <f t="shared" ref="O15:O16" si="5">N15/60</f>
-        <v>0.9900000000000001</v>
+        <f>N15/80</f>
+        <v>0.99</v>
       </c>
     </row>
     <row r="16" spans="2:15" x14ac:dyDescent="0.2">
@@ -914,6 +944,9 @@
       </c>
       <c r="D16">
         <v>79</v>
+      </c>
+      <c r="E16">
+        <v>85</v>
       </c>
       <c r="G16">
         <v>96</v>
@@ -928,7 +961,7 @@
       </c>
       <c r="K16">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="L16">
         <f t="shared" si="4"/>
@@ -940,14 +973,14 @@
       </c>
       <c r="N16">
         <f t="shared" si="1"/>
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="O16" s="2">
-        <f t="shared" si="5"/>
-        <v>0.8833333333333333</v>
-      </c>
-    </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.2">
+        <f t="shared" ref="O15:O16" si="5">N16/80</f>
+        <v>0.88749999999999996</v>
+      </c>
+    </row>
+    <row r="18" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B18" t="s">
         <v>15</v>
       </c>
@@ -959,9 +992,9 @@
         <f>AVERAGE(D6:D16)</f>
         <v>86.555555555555557</v>
       </c>
-      <c r="E18" s="1" t="e">
+      <c r="E18" s="1">
         <f>AVERAGE(E6:E16)</f>
-        <v>#DIV/0!</v>
+        <v>86.666666666666671</v>
       </c>
       <c r="F18" s="1" t="e">
         <f>AVERAGE(F6:F16)</f>
@@ -971,8 +1004,15 @@
         <f>AVERAGE(G6:G16)</f>
         <v>96.222222222222229</v>
       </c>
-    </row>
-    <row r="19" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="N18" t="s">
+        <v>24</v>
+      </c>
+      <c r="O18" s="2">
+        <f>AVERAGE(O6:O16)</f>
+        <v>0.92499999999999993</v>
+      </c>
+    </row>
+    <row r="19" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B19" t="s">
         <v>23</v>
       </c>
@@ -984,11 +1024,24 @@
         <f>STDEV(D6:D16)</f>
         <v>10.654941472283054</v>
       </c>
-      <c r="E19" s="1"/>
+      <c r="E19" s="1">
+        <f>STDEV(E6:E16)</f>
+        <v>5.8094750193111251</v>
+      </c>
       <c r="F19" s="1"/>
-      <c r="G19" s="1"/>
-    </row>
-    <row r="20" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="G19" s="1">
+        <f>STDEV(G6:G16)</f>
+        <v>1.922093765778466</v>
+      </c>
+      <c r="N19" t="s">
+        <v>25</v>
+      </c>
+      <c r="O19" s="2">
+        <f>STDEV(O6:O16)</f>
+        <v>5.7973593126526113E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B20" t="s">
         <v>16</v>
       </c>
@@ -998,8 +1051,11 @@
       <c r="D20">
         <v>5</v>
       </c>
-    </row>
-    <row r="21" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="E20">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B21" t="s">
         <v>17</v>
       </c>
@@ -1011,9 +1067,9 @@
         <f>D18+D20</f>
         <v>91.555555555555557</v>
       </c>
-      <c r="E21" s="1" t="e">
+      <c r="E21" s="1">
         <f t="shared" ref="E21:G21" si="6">E18+E20</f>
-        <v>#DIV/0!</v>
+        <v>91.666666666666671</v>
       </c>
       <c r="F21" s="1" t="e">
         <f t="shared" si="6"/>
@@ -1024,7 +1080,7 @@
         <v>96.222222222222229</v>
       </c>
     </row>
-    <row r="26" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B26" t="s">
         <v>10</v>
       </c>
@@ -1059,7 +1115,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="27" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B27">
         <v>1</v>
       </c>
@@ -1094,7 +1150,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="28" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B28">
         <v>2</v>
       </c>
@@ -1129,7 +1185,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="29" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B29">
         <v>3</v>
       </c>
@@ -1164,7 +1220,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="30" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B30">
         <v>4</v>
       </c>
@@ -1199,7 +1255,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="31" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B31">
         <v>5</v>
       </c>
@@ -1234,7 +1290,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="32" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B32">
         <v>6</v>
       </c>
@@ -1926,6 +1982,33 @@
       <c r="C53">
         <v>6</v>
       </c>
+      <c r="D53">
+        <v>6</v>
+      </c>
+      <c r="E53">
+        <v>6</v>
+      </c>
+      <c r="F53">
+        <v>6</v>
+      </c>
+      <c r="G53">
+        <v>6</v>
+      </c>
+      <c r="H53">
+        <v>6</v>
+      </c>
+      <c r="I53">
+        <v>6</v>
+      </c>
+      <c r="J53">
+        <v>6</v>
+      </c>
+      <c r="K53">
+        <v>6</v>
+      </c>
+      <c r="L53">
+        <v>6</v>
+      </c>
     </row>
     <row r="54" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B54">
@@ -1934,6 +2017,33 @@
       <c r="C54">
         <v>6</v>
       </c>
+      <c r="D54">
+        <v>6</v>
+      </c>
+      <c r="E54">
+        <v>6</v>
+      </c>
+      <c r="F54">
+        <v>6</v>
+      </c>
+      <c r="G54">
+        <v>2</v>
+      </c>
+      <c r="H54">
+        <v>2</v>
+      </c>
+      <c r="I54">
+        <v>6</v>
+      </c>
+      <c r="J54">
+        <v>4</v>
+      </c>
+      <c r="K54">
+        <v>6</v>
+      </c>
+      <c r="L54">
+        <v>4</v>
+      </c>
     </row>
     <row r="55" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B55">
@@ -1942,6 +2052,33 @@
       <c r="C55">
         <v>6</v>
       </c>
+      <c r="D55">
+        <v>4</v>
+      </c>
+      <c r="E55">
+        <v>4</v>
+      </c>
+      <c r="F55">
+        <v>3</v>
+      </c>
+      <c r="G55">
+        <v>2</v>
+      </c>
+      <c r="H55">
+        <v>2</v>
+      </c>
+      <c r="I55">
+        <v>6</v>
+      </c>
+      <c r="J55">
+        <v>4</v>
+      </c>
+      <c r="K55">
+        <v>6</v>
+      </c>
+      <c r="L55">
+        <v>6</v>
+      </c>
     </row>
     <row r="56" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B56">
@@ -1950,6 +2087,33 @@
       <c r="C56">
         <v>6</v>
       </c>
+      <c r="D56">
+        <v>6</v>
+      </c>
+      <c r="E56">
+        <v>6</v>
+      </c>
+      <c r="F56">
+        <v>5</v>
+      </c>
+      <c r="G56">
+        <v>6</v>
+      </c>
+      <c r="H56">
+        <v>5</v>
+      </c>
+      <c r="I56">
+        <v>6</v>
+      </c>
+      <c r="J56">
+        <v>5</v>
+      </c>
+      <c r="K56">
+        <v>6</v>
+      </c>
+      <c r="L56">
+        <v>5</v>
+      </c>
     </row>
     <row r="57" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B57">
@@ -1958,6 +2122,33 @@
       <c r="C57">
         <v>16</v>
       </c>
+      <c r="D57">
+        <v>15</v>
+      </c>
+      <c r="E57">
+        <v>10</v>
+      </c>
+      <c r="F57">
+        <v>13</v>
+      </c>
+      <c r="G57">
+        <v>11</v>
+      </c>
+      <c r="H57">
+        <v>13</v>
+      </c>
+      <c r="I57">
+        <v>11</v>
+      </c>
+      <c r="J57">
+        <v>16</v>
+      </c>
+      <c r="K57">
+        <v>14</v>
+      </c>
+      <c r="L57">
+        <v>11</v>
+      </c>
     </row>
     <row r="58" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B58">
@@ -1966,6 +2157,33 @@
       <c r="C58">
         <v>6</v>
       </c>
+      <c r="D58">
+        <v>6</v>
+      </c>
+      <c r="E58">
+        <v>6</v>
+      </c>
+      <c r="F58">
+        <v>6</v>
+      </c>
+      <c r="G58">
+        <v>6</v>
+      </c>
+      <c r="H58">
+        <v>6</v>
+      </c>
+      <c r="I58">
+        <v>6</v>
+      </c>
+      <c r="J58">
+        <v>6</v>
+      </c>
+      <c r="K58">
+        <v>6</v>
+      </c>
+      <c r="L58">
+        <v>6</v>
+      </c>
     </row>
     <row r="59" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B59">
@@ -1974,6 +2192,33 @@
       <c r="C59">
         <v>12</v>
       </c>
+      <c r="D59">
+        <v>12</v>
+      </c>
+      <c r="E59">
+        <v>10</v>
+      </c>
+      <c r="F59">
+        <v>12</v>
+      </c>
+      <c r="G59">
+        <v>12</v>
+      </c>
+      <c r="H59">
+        <v>6</v>
+      </c>
+      <c r="I59">
+        <v>8</v>
+      </c>
+      <c r="J59">
+        <v>10</v>
+      </c>
+      <c r="K59">
+        <v>10</v>
+      </c>
+      <c r="L59">
+        <v>9</v>
+      </c>
     </row>
     <row r="60" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B60">
@@ -1982,6 +2227,33 @@
       <c r="C60">
         <v>8</v>
       </c>
+      <c r="D60">
+        <v>8</v>
+      </c>
+      <c r="E60">
+        <v>8</v>
+      </c>
+      <c r="F60">
+        <v>8</v>
+      </c>
+      <c r="G60">
+        <v>8</v>
+      </c>
+      <c r="H60">
+        <v>7</v>
+      </c>
+      <c r="I60">
+        <v>8</v>
+      </c>
+      <c r="J60">
+        <v>6</v>
+      </c>
+      <c r="K60">
+        <v>8</v>
+      </c>
+      <c r="L60">
+        <v>8</v>
+      </c>
     </row>
     <row r="61" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B61">
@@ -1990,12 +2262,66 @@
       <c r="C61">
         <v>10</v>
       </c>
+      <c r="D61">
+        <v>10</v>
+      </c>
+      <c r="E61">
+        <v>10</v>
+      </c>
+      <c r="F61">
+        <v>10</v>
+      </c>
+      <c r="G61">
+        <v>10</v>
+      </c>
+      <c r="H61">
+        <v>10</v>
+      </c>
+      <c r="I61">
+        <v>5</v>
+      </c>
+      <c r="J61">
+        <v>5</v>
+      </c>
+      <c r="K61">
+        <v>10</v>
+      </c>
+      <c r="L61">
+        <v>10</v>
+      </c>
     </row>
     <row r="62" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B62">
         <v>10</v>
       </c>
       <c r="C62">
+        <v>10</v>
+      </c>
+      <c r="D62">
+        <v>10</v>
+      </c>
+      <c r="E62">
+        <v>10</v>
+      </c>
+      <c r="F62">
+        <v>10</v>
+      </c>
+      <c r="G62">
+        <v>10</v>
+      </c>
+      <c r="H62">
+        <v>10</v>
+      </c>
+      <c r="I62">
+        <v>10</v>
+      </c>
+      <c r="J62">
+        <v>10</v>
+      </c>
+      <c r="K62">
+        <v>10</v>
+      </c>
+      <c r="L62">
         <v>10</v>
       </c>
     </row>
@@ -2006,6 +2332,33 @@
       <c r="C63">
         <v>6</v>
       </c>
+      <c r="D63">
+        <v>6</v>
+      </c>
+      <c r="E63">
+        <v>6</v>
+      </c>
+      <c r="F63">
+        <v>4</v>
+      </c>
+      <c r="G63">
+        <v>4</v>
+      </c>
+      <c r="H63">
+        <v>5</v>
+      </c>
+      <c r="I63">
+        <v>6</v>
+      </c>
+      <c r="J63">
+        <v>5</v>
+      </c>
+      <c r="K63">
+        <v>4</v>
+      </c>
+      <c r="L63">
+        <v>4</v>
+      </c>
     </row>
     <row r="64" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B64">
@@ -2014,6 +2367,33 @@
       <c r="C64">
         <v>8</v>
       </c>
+      <c r="D64">
+        <v>6</v>
+      </c>
+      <c r="E64">
+        <v>7</v>
+      </c>
+      <c r="F64">
+        <v>7</v>
+      </c>
+      <c r="G64">
+        <v>6</v>
+      </c>
+      <c r="H64">
+        <v>5</v>
+      </c>
+      <c r="I64">
+        <v>5</v>
+      </c>
+      <c r="J64">
+        <v>7</v>
+      </c>
+      <c r="K64">
+        <v>8</v>
+      </c>
+      <c r="L64">
+        <v>6</v>
+      </c>
     </row>
     <row r="65" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B65" t="s">
@@ -2025,39 +2405,39 @@
       </c>
       <c r="D65">
         <f t="shared" ref="D65:L65" si="9">SUM(D53:D64)</f>
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="E65">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="F65">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="G65">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="H65">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="I65">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="J65">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="K65">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="L65">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>85</v>
       </c>
     </row>
   </sheetData>

--- a/Advanced Reactor Materials/Fall2025/grading.xlsx
+++ b/Advanced Reactor Materials/Fall2025/grading.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11102"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11116"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/beelbw/projects/TEACHING/Advanced Reactor Materials/Fall2025/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/benjaminbeeler/projects/TEACHING/Advanced Reactor Materials/Fall2025/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1A5EEDB-2619-F14C-88F2-787B94D06C47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44DB959C-16F1-7C4D-89C4-74EA011046E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3100" yWindow="4200" windowWidth="24220" windowHeight="17440" xr2:uid="{4E6CEA4E-2509-754B-9890-44C713F10933}"/>
+    <workbookView xWindow="3100" yWindow="3820" windowWidth="24220" windowHeight="17440" xr2:uid="{4E6CEA4E-2509-754B-9890-44C713F10933}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="27">
   <si>
     <t>Roster</t>
   </si>
@@ -114,6 +114,9 @@
   </si>
   <si>
     <t>stdev</t>
+  </si>
+  <si>
+    <t>survery bonus</t>
   </si>
 </sst>
 </file>
@@ -490,7 +493,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7A9E859-0099-8A4F-9892-6572C8559B21}">
-  <dimension ref="B2:O65"/>
+  <dimension ref="B2:O81"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="20.1640625" customWidth="1"/>
@@ -976,7 +979,7 @@
         <v>71</v>
       </c>
       <c r="O16" s="2">
-        <f t="shared" ref="O15:O16" si="5">N16/80</f>
+        <f t="shared" ref="O16" si="5">N16/80</f>
         <v>0.88749999999999996</v>
       </c>
     </row>
@@ -1942,7 +1945,7 @@
     </row>
     <row r="52" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B52" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C52" t="s">
         <v>18</v>
@@ -2438,6 +2441,190 @@
       <c r="L65">
         <f t="shared" si="9"/>
         <v>85</v>
+      </c>
+    </row>
+    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B67" t="s">
+        <v>13</v>
+      </c>
+      <c r="C67" t="s">
+        <v>18</v>
+      </c>
+      <c r="D67" t="s">
+        <v>1</v>
+      </c>
+      <c r="E67" t="s">
+        <v>2</v>
+      </c>
+      <c r="F67" t="s">
+        <v>20</v>
+      </c>
+      <c r="G67" t="s">
+        <v>5</v>
+      </c>
+      <c r="H67" t="s">
+        <v>6</v>
+      </c>
+      <c r="I67" t="s">
+        <v>8</v>
+      </c>
+      <c r="J67" t="s">
+        <v>9</v>
+      </c>
+      <c r="K67" t="s">
+        <v>4</v>
+      </c>
+      <c r="L67" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B68">
+        <v>1</v>
+      </c>
+      <c r="C68">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B69">
+        <v>2</v>
+      </c>
+      <c r="C69">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B70">
+        <v>3</v>
+      </c>
+      <c r="C70">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B71">
+        <v>4</v>
+      </c>
+      <c r="C71">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B72">
+        <v>5</v>
+      </c>
+      <c r="C72">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B73">
+        <v>6</v>
+      </c>
+      <c r="C73">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B74">
+        <v>7</v>
+      </c>
+      <c r="C74">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B75">
+        <v>8</v>
+      </c>
+      <c r="C75">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B76">
+        <v>9</v>
+      </c>
+      <c r="C76">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B77">
+        <v>10</v>
+      </c>
+      <c r="C77">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="78" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B78">
+        <v>11</v>
+      </c>
+      <c r="C78">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B79">
+        <v>12</v>
+      </c>
+      <c r="C79">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B80" t="s">
+        <v>26</v>
+      </c>
+      <c r="G80">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="81" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B81" t="s">
+        <v>21</v>
+      </c>
+      <c r="C81">
+        <f>SUM(C68:C79)</f>
+        <v>100</v>
+      </c>
+      <c r="D81">
+        <f t="shared" ref="D81:L81" si="10">SUM(D68:D79)</f>
+        <v>0</v>
+      </c>
+      <c r="E81">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="F81">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="G81">
+        <f>SUM(G68:G80)</f>
+        <v>5</v>
+      </c>
+      <c r="H81">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="I81">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="K81">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="L81">
+        <f t="shared" si="10"/>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Advanced Reactor Materials/Fall2025/grading.xlsx
+++ b/Advanced Reactor Materials/Fall2025/grading.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/benjaminbeeler/projects/TEACHING/Advanced Reactor Materials/Fall2025/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/beelbw/projects/TEACHING/Advanced Reactor Materials/Fall2025/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44DB959C-16F1-7C4D-89C4-74EA011046E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CB5640F-E09A-EB4B-B126-A045613CC45B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3100" yWindow="3820" windowWidth="24220" windowHeight="17440" xr2:uid="{4E6CEA4E-2509-754B-9890-44C713F10933}"/>
   </bookViews>
@@ -116,7 +116,7 @@
     <t>stdev</t>
   </si>
   <si>
-    <t>survery bonus</t>
+    <t>survey bonus</t>
   </si>
 </sst>
 </file>
@@ -2483,7 +2483,7 @@
         <v>1</v>
       </c>
       <c r="C68">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="69" spans="2:12" x14ac:dyDescent="0.2">
@@ -2491,7 +2491,7 @@
         <v>2</v>
       </c>
       <c r="C69">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="70" spans="2:12" x14ac:dyDescent="0.2">
@@ -2499,7 +2499,7 @@
         <v>3</v>
       </c>
       <c r="C70">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="71" spans="2:12" x14ac:dyDescent="0.2">
@@ -2507,7 +2507,7 @@
         <v>4</v>
       </c>
       <c r="C71">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="72" spans="2:12" x14ac:dyDescent="0.2">
@@ -2515,7 +2515,7 @@
         <v>5</v>
       </c>
       <c r="C72">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="73" spans="2:12" x14ac:dyDescent="0.2">
@@ -2523,7 +2523,7 @@
         <v>6</v>
       </c>
       <c r="C73">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="74" spans="2:12" x14ac:dyDescent="0.2">
@@ -2539,7 +2539,7 @@
         <v>8</v>
       </c>
       <c r="C75">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="76" spans="2:12" x14ac:dyDescent="0.2">
@@ -2547,7 +2547,7 @@
         <v>9</v>
       </c>
       <c r="C76">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="77" spans="2:12" x14ac:dyDescent="0.2">
@@ -2563,7 +2563,7 @@
         <v>11</v>
       </c>
       <c r="C78">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="79" spans="2:12" x14ac:dyDescent="0.2">
@@ -2571,7 +2571,7 @@
         <v>12</v>
       </c>
       <c r="C79">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="80" spans="2:12" x14ac:dyDescent="0.2">
@@ -2579,6 +2579,12 @@
         <v>26</v>
       </c>
       <c r="G80">
+        <v>5</v>
+      </c>
+      <c r="H80">
+        <v>5</v>
+      </c>
+      <c r="I80">
         <v>5</v>
       </c>
     </row>

--- a/Advanced Reactor Materials/Fall2025/grading.xlsx
+++ b/Advanced Reactor Materials/Fall2025/grading.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11116"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11122"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/beelbw/projects/TEACHING/Advanced Reactor Materials/Fall2025/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/benjaminbeeler/projects/TEACHING/Advanced Reactor Materials/Fall2025/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CB5640F-E09A-EB4B-B126-A045613CC45B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09AAEAEB-14BE-294E-8235-E882699900CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3100" yWindow="3820" windowWidth="24220" windowHeight="17440" xr2:uid="{4E6CEA4E-2509-754B-9890-44C713F10933}"/>
   </bookViews>
@@ -2578,6 +2578,9 @@
       <c r="B80" t="s">
         <v>26</v>
       </c>
+      <c r="F80">
+        <v>5</v>
+      </c>
       <c r="G80">
         <v>5</v>
       </c>
@@ -2585,6 +2588,12 @@
         <v>5</v>
       </c>
       <c r="I80">
+        <v>5</v>
+      </c>
+      <c r="K80">
+        <v>5</v>
+      </c>
+      <c r="L80">
         <v>5</v>
       </c>
     </row>

--- a/Advanced Reactor Materials/Fall2025/grading.xlsx
+++ b/Advanced Reactor Materials/Fall2025/grading.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/benjaminbeeler/projects/TEACHING/Advanced Reactor Materials/Fall2025/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/beelbw/projects/TEACHING/Advanced Reactor Materials/Fall2025/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09AAEAEB-14BE-294E-8235-E882699900CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B6D5ED5-7BF8-4A4B-B5A6-17BEF3C72EFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3100" yWindow="3820" windowWidth="24220" windowHeight="17440" xr2:uid="{4E6CEA4E-2509-754B-9890-44C713F10933}"/>
   </bookViews>
@@ -2578,6 +2578,9 @@
       <c r="B80" t="s">
         <v>26</v>
       </c>
+      <c r="D80">
+        <v>5</v>
+      </c>
       <c r="F80">
         <v>5</v>
       </c>
@@ -2606,8 +2609,8 @@
         <v>100</v>
       </c>
       <c r="D81">
-        <f t="shared" ref="D81:L81" si="10">SUM(D68:D79)</f>
-        <v>0</v>
+        <f t="shared" ref="D81:F81" si="10">SUM(D68:D80)</f>
+        <v>5</v>
       </c>
       <c r="E81">
         <f t="shared" si="10"/>
@@ -2615,31 +2618,31 @@
       </c>
       <c r="F81">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G81">
         <f>SUM(G68:G80)</f>
         <v>5</v>
       </c>
       <c r="H81">
-        <f t="shared" si="10"/>
+        <f t="shared" ref="H81:L81" si="11">SUM(H68:H80)</f>
+        <v>5</v>
+      </c>
+      <c r="I81">
+        <f t="shared" si="11"/>
+        <v>5</v>
+      </c>
+      <c r="J81">
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="I81">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="J81">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
       <c r="K81">
-        <f t="shared" si="10"/>
-        <v>0</v>
+        <f t="shared" si="11"/>
+        <v>5</v>
       </c>
       <c r="L81">
-        <f t="shared" si="10"/>
-        <v>0</v>
+        <f t="shared" si="11"/>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/Advanced Reactor Materials/Fall2025/grading.xlsx
+++ b/Advanced Reactor Materials/Fall2025/grading.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11122"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11130"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/beelbw/projects/TEACHING/Advanced Reactor Materials/Fall2025/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/benjaminbeeler/projects/TEACHING/Advanced Reactor Materials/Fall2025/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B6D5ED5-7BF8-4A4B-B5A6-17BEF3C72EFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50714F41-EAB6-064B-B44A-CD9B3F78579F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3100" yWindow="3820" windowWidth="24220" windowHeight="17440" xr2:uid="{4E6CEA4E-2509-754B-9890-44C713F10933}"/>
+    <workbookView xWindow="16040" yWindow="3800" windowWidth="24220" windowHeight="17440" xr2:uid="{4E6CEA4E-2509-754B-9890-44C713F10933}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="35">
   <si>
     <t>Roster</t>
   </si>
@@ -117,6 +117,30 @@
   </si>
   <si>
     <t>survey bonus</t>
+  </si>
+  <si>
+    <t>Survey Bonus</t>
+  </si>
+  <si>
+    <t>Letter</t>
+  </si>
+  <si>
+    <t>A+</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>B-</t>
+  </si>
+  <si>
+    <t>A-</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>B+</t>
   </si>
 </sst>
 </file>
@@ -155,10 +179,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -174,6 +199,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -493,7 +522,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7A9E859-0099-8A4F-9892-6572C8559B21}">
-  <dimension ref="B2:O81"/>
+  <dimension ref="B2:P83"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="20.1640625" customWidth="1"/>
@@ -501,12 +530,12 @@
     <col min="9" max="9" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C3">
         <v>0.2</v>
       </c>
@@ -523,12 +552,12 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="4" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:16" x14ac:dyDescent="0.2">
       <c r="I4" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B5" t="s">
         <v>0</v>
       </c>
@@ -568,8 +597,11 @@
       <c r="O5" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="6" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B6" t="s">
         <v>1</v>
       </c>
@@ -581,6 +613,9 @@
       </c>
       <c r="E6">
         <v>95</v>
+      </c>
+      <c r="F6">
+        <v>92</v>
       </c>
       <c r="G6">
         <v>100</v>
@@ -598,23 +633,26 @@
         <v>20</v>
       </c>
       <c r="L6">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>(F6+F$20+$F$21)*F$3</f>
+        <v>20.8</v>
       </c>
       <c r="M6">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="N6">
+      <c r="N6" s="3">
         <f>SUM(I6:M6)</f>
-        <v>79</v>
+        <v>99.8</v>
       </c>
       <c r="O6" s="2">
-        <f>N6/80</f>
-        <v>0.98750000000000004</v>
-      </c>
-    </row>
-    <row r="7" spans="2:15" x14ac:dyDescent="0.2">
+        <f>N6/100</f>
+        <v>0.998</v>
+      </c>
+      <c r="P6" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B7" t="s">
         <v>2</v>
       </c>
@@ -626,6 +664,9 @@
       </c>
       <c r="E7">
         <v>89</v>
+      </c>
+      <c r="F7">
+        <v>90</v>
       </c>
       <c r="G7">
         <v>95</v>
@@ -643,23 +684,26 @@
         <v>18.8</v>
       </c>
       <c r="L7">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f t="shared" ref="L7:L12" si="1">(F7+F$20+$F$21)*F$3</f>
+        <v>20.400000000000002</v>
       </c>
       <c r="M7">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="N7">
-        <f t="shared" ref="N7:N16" si="1">SUM(I7:M7)</f>
-        <v>76.2</v>
+      <c r="N7" s="3">
+        <f t="shared" ref="N7:N16" si="2">SUM(I7:M7)</f>
+        <v>96.600000000000009</v>
       </c>
       <c r="O7" s="2">
-        <f t="shared" ref="O7:O12" si="2">N7/80</f>
-        <v>0.95250000000000001</v>
-      </c>
-    </row>
-    <row r="8" spans="2:15" x14ac:dyDescent="0.2">
+        <f t="shared" ref="O7:O12" si="3">N7/100</f>
+        <v>0.96600000000000008</v>
+      </c>
+      <c r="P7" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="8" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B8" t="s">
         <v>20</v>
       </c>
@@ -671,6 +715,9 @@
       </c>
       <c r="E8">
         <v>90</v>
+      </c>
+      <c r="F8">
+        <v>84</v>
       </c>
       <c r="G8">
         <v>96</v>
@@ -688,23 +735,26 @@
         <v>19</v>
       </c>
       <c r="L8">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>19.200000000000003</v>
       </c>
       <c r="M8">
         <f t="shared" si="0"/>
         <v>19.200000000000003</v>
       </c>
-      <c r="N8">
-        <f t="shared" ref="N8" si="3">SUM(I8:M8)</f>
-        <v>76</v>
+      <c r="N8" s="3">
+        <f t="shared" ref="N8" si="4">SUM(I8:M8)</f>
+        <v>95.2</v>
       </c>
       <c r="O8" s="2">
-        <f t="shared" si="2"/>
-        <v>0.95</v>
-      </c>
-    </row>
-    <row r="9" spans="2:15" x14ac:dyDescent="0.2">
+        <f t="shared" si="3"/>
+        <v>0.95200000000000007</v>
+      </c>
+      <c r="P8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B9" t="s">
         <v>5</v>
       </c>
@@ -716,6 +766,9 @@
       </c>
       <c r="E9">
         <v>83</v>
+      </c>
+      <c r="F9">
+        <v>74</v>
       </c>
       <c r="G9">
         <v>96</v>
@@ -733,23 +786,26 @@
         <v>17.600000000000001</v>
       </c>
       <c r="L9">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>(F9+F$20+$F$21)*F$3</f>
+        <v>17.2</v>
       </c>
       <c r="M9">
         <f t="shared" si="0"/>
         <v>19.200000000000003</v>
       </c>
-      <c r="N9">
-        <f t="shared" si="1"/>
-        <v>68.600000000000009</v>
+      <c r="N9" s="3">
+        <f t="shared" si="2"/>
+        <v>85.800000000000011</v>
       </c>
       <c r="O9" s="2">
-        <f t="shared" si="2"/>
-        <v>0.85750000000000015</v>
-      </c>
-    </row>
-    <row r="10" spans="2:15" x14ac:dyDescent="0.2">
+        <f t="shared" si="3"/>
+        <v>0.8580000000000001</v>
+      </c>
+      <c r="P9" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B10" t="s">
         <v>6</v>
       </c>
@@ -761,6 +817,9 @@
       </c>
       <c r="E10">
         <v>77</v>
+      </c>
+      <c r="F10">
+        <v>68</v>
       </c>
       <c r="G10">
         <v>93</v>
@@ -778,23 +837,26 @@
         <v>16.400000000000002</v>
       </c>
       <c r="L10">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>16</v>
       </c>
       <c r="M10">
         <f t="shared" si="0"/>
         <v>18.600000000000001</v>
       </c>
-      <c r="N10">
-        <f t="shared" si="1"/>
-        <v>65.800000000000011</v>
+      <c r="N10" s="3">
+        <f t="shared" si="2"/>
+        <v>81.800000000000011</v>
       </c>
       <c r="O10" s="2">
-        <f t="shared" si="2"/>
-        <v>0.82250000000000012</v>
-      </c>
-    </row>
-    <row r="11" spans="2:15" x14ac:dyDescent="0.2">
+        <f t="shared" si="3"/>
+        <v>0.81800000000000006</v>
+      </c>
+      <c r="P10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="11" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B11" t="s">
         <v>8</v>
       </c>
@@ -806,6 +868,9 @@
       </c>
       <c r="E11">
         <v>83</v>
+      </c>
+      <c r="F11">
+        <v>81</v>
       </c>
       <c r="G11">
         <v>96</v>
@@ -823,23 +888,26 @@
         <v>17.600000000000001</v>
       </c>
       <c r="L11">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>18.600000000000001</v>
       </c>
       <c r="M11">
         <f t="shared" si="0"/>
         <v>19.200000000000003</v>
       </c>
-      <c r="N11">
-        <f t="shared" si="1"/>
-        <v>73.800000000000011</v>
+      <c r="N11" s="3">
+        <f t="shared" si="2"/>
+        <v>92.4</v>
       </c>
       <c r="O11" s="2">
-        <f t="shared" si="2"/>
-        <v>0.9225000000000001</v>
-      </c>
-    </row>
-    <row r="12" spans="2:15" x14ac:dyDescent="0.2">
+        <f t="shared" si="3"/>
+        <v>0.92400000000000004</v>
+      </c>
+      <c r="P11" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="12" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B12" t="s">
         <v>9</v>
       </c>
@@ -851,6 +919,9 @@
       </c>
       <c r="E12">
         <v>84</v>
+      </c>
+      <c r="F12">
+        <v>85</v>
       </c>
       <c r="G12">
         <v>98</v>
@@ -868,32 +939,37 @@
         <v>17.8</v>
       </c>
       <c r="L12">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>(F12+F$20+$F$21)*F$3</f>
+        <v>19.400000000000002</v>
       </c>
       <c r="M12">
         <f t="shared" si="0"/>
         <v>19.600000000000001</v>
       </c>
-      <c r="N12">
-        <f t="shared" si="1"/>
-        <v>76.400000000000006</v>
+      <c r="N12" s="3">
+        <f t="shared" si="2"/>
+        <v>95.800000000000011</v>
       </c>
       <c r="O12" s="2">
-        <f t="shared" si="2"/>
-        <v>0.95500000000000007</v>
-      </c>
-    </row>
-    <row r="13" spans="2:15" x14ac:dyDescent="0.2">
+        <f t="shared" si="3"/>
+        <v>0.95800000000000007</v>
+      </c>
+      <c r="P12" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="13" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="N13" s="3"/>
       <c r="O13" s="2"/>
     </row>
-    <row r="14" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B14" t="s">
         <v>3</v>
       </c>
+      <c r="N14" s="3"/>
       <c r="O14" s="2"/>
     </row>
-    <row r="15" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B15" t="s">
         <v>4</v>
       </c>
@@ -906,39 +982,45 @@
       <c r="E15">
         <v>94</v>
       </c>
+      <c r="F15">
+        <v>95</v>
+      </c>
       <c r="G15">
         <v>96</v>
       </c>
       <c r="I15">
-        <f t="shared" ref="I15:M16" si="4">(C15+C$20)*C$3</f>
+        <f t="shared" ref="I15:M16" si="5">(C15+C$20)*C$3</f>
         <v>19.8</v>
       </c>
       <c r="J15">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>20.400000000000002</v>
       </c>
       <c r="K15">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>19.8</v>
       </c>
       <c r="L15">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <f>(F15+F$20+$F$21)*F$3</f>
+        <v>21.400000000000002</v>
       </c>
       <c r="M15">
-        <f t="shared" si="4"/>
+        <f>(G15+G$20)*G$3</f>
         <v>19.200000000000003</v>
       </c>
-      <c r="N15">
+      <c r="N15" s="3">
         <f>SUM(I15:M15)</f>
-        <v>79.2</v>
+        <v>100.60000000000001</v>
       </c>
       <c r="O15" s="2">
-        <f>N15/80</f>
-        <v>0.99</v>
-      </c>
-    </row>
-    <row r="16" spans="2:15" x14ac:dyDescent="0.2">
+        <f t="shared" ref="O15:O16" si="6">N15/100</f>
+        <v>1.006</v>
+      </c>
+      <c r="P15" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="16" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B16" t="s">
         <v>7</v>
       </c>
@@ -951,36 +1033,42 @@
       <c r="E16">
         <v>85</v>
       </c>
+      <c r="F16">
+        <v>78</v>
+      </c>
       <c r="G16">
         <v>96</v>
       </c>
       <c r="I16">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>17</v>
       </c>
       <c r="J16">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>16.8</v>
       </c>
       <c r="K16">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>18</v>
       </c>
       <c r="L16">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <f>(F16+F$20+$F$21)*F$3</f>
+        <v>18</v>
       </c>
       <c r="M16">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>19.200000000000003</v>
       </c>
-      <c r="N16">
-        <f t="shared" si="1"/>
-        <v>71</v>
+      <c r="N16" s="3">
+        <f t="shared" si="2"/>
+        <v>89</v>
       </c>
       <c r="O16" s="2">
-        <f t="shared" ref="O16" si="5">N16/80</f>
-        <v>0.88749999999999996</v>
+        <f t="shared" si="6"/>
+        <v>0.89</v>
+      </c>
+      <c r="P16" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="18" spans="2:15" x14ac:dyDescent="0.2">
@@ -999,9 +1087,9 @@
         <f>AVERAGE(E6:E16)</f>
         <v>86.666666666666671</v>
       </c>
-      <c r="F18" s="1" t="e">
+      <c r="F18" s="1">
         <f>AVERAGE(F6:F16)</f>
-        <v>#DIV/0!</v>
+        <v>83</v>
       </c>
       <c r="G18" s="1">
         <f>AVERAGE(G6:G16)</f>
@@ -1012,7 +1100,7 @@
       </c>
       <c r="O18" s="2">
         <f>AVERAGE(O6:O16)</f>
-        <v>0.92499999999999993</v>
+        <v>0.93000000000000016</v>
       </c>
     </row>
     <row r="19" spans="2:15" x14ac:dyDescent="0.2">
@@ -1031,7 +1119,10 @@
         <f>STDEV(E6:E16)</f>
         <v>5.8094750193111251</v>
       </c>
-      <c r="F19" s="1"/>
+      <c r="F19" s="1">
+        <f>STDEV(F6:F16)</f>
+        <v>8.7607077339676156</v>
+      </c>
       <c r="G19" s="1">
         <f>STDEV(G6:G16)</f>
         <v>1.922093765778466</v>
@@ -1041,7 +1132,7 @@
       </c>
       <c r="O19" s="2">
         <f>STDEV(O6:O16)</f>
-        <v>5.7973593126526113E-2</v>
+        <v>6.3568860301251265E-2</v>
       </c>
     </row>
     <row r="20" spans="2:15" x14ac:dyDescent="0.2">
@@ -1057,29 +1148,40 @@
       <c r="E20">
         <v>5</v>
       </c>
+      <c r="F20">
+        <v>7</v>
+      </c>
     </row>
     <row r="21" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B21" t="s">
+        <v>27</v>
+      </c>
+      <c r="F21">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B22" t="s">
         <v>17</v>
       </c>
-      <c r="C21" s="1">
+      <c r="C22" s="1">
         <f>C18+C20</f>
         <v>90.555555555555557</v>
       </c>
-      <c r="D21" s="1">
+      <c r="D22" s="1">
         <f>D18+D20</f>
         <v>91.555555555555557</v>
       </c>
-      <c r="E21" s="1">
-        <f t="shared" ref="E21:G21" si="6">E18+E20</f>
+      <c r="E22" s="1">
+        <f>E18+E20</f>
         <v>91.666666666666671</v>
       </c>
-      <c r="F21" s="1" t="e">
-        <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G21" s="1">
-        <f t="shared" si="6"/>
+      <c r="F22" s="1">
+        <f>F18+F20+F21</f>
+        <v>95</v>
+      </c>
+      <c r="G22" s="1">
+        <f>G18+G20</f>
         <v>96.222222222222229</v>
       </c>
     </row>
@@ -2485,6 +2587,33 @@
       <c r="C68">
         <v>10</v>
       </c>
+      <c r="D68">
+        <v>10</v>
+      </c>
+      <c r="E68">
+        <v>9</v>
+      </c>
+      <c r="F68">
+        <v>10</v>
+      </c>
+      <c r="G68">
+        <v>9</v>
+      </c>
+      <c r="H68">
+        <v>6</v>
+      </c>
+      <c r="I68">
+        <v>9</v>
+      </c>
+      <c r="J68">
+        <v>10</v>
+      </c>
+      <c r="K68">
+        <v>10</v>
+      </c>
+      <c r="L68">
+        <v>9</v>
+      </c>
     </row>
     <row r="69" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B69">
@@ -2493,6 +2622,33 @@
       <c r="C69">
         <v>10</v>
       </c>
+      <c r="D69">
+        <v>7</v>
+      </c>
+      <c r="E69">
+        <v>7</v>
+      </c>
+      <c r="F69">
+        <v>7</v>
+      </c>
+      <c r="G69">
+        <v>7</v>
+      </c>
+      <c r="H69">
+        <v>10</v>
+      </c>
+      <c r="I69">
+        <v>10</v>
+      </c>
+      <c r="J69">
+        <v>10</v>
+      </c>
+      <c r="K69">
+        <v>10</v>
+      </c>
+      <c r="L69">
+        <v>7</v>
+      </c>
     </row>
     <row r="70" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B70">
@@ -2501,6 +2657,33 @@
       <c r="C70">
         <v>10</v>
       </c>
+      <c r="D70">
+        <v>8</v>
+      </c>
+      <c r="E70">
+        <v>9</v>
+      </c>
+      <c r="F70">
+        <v>10</v>
+      </c>
+      <c r="G70">
+        <v>5</v>
+      </c>
+      <c r="H70">
+        <v>7</v>
+      </c>
+      <c r="I70">
+        <v>7</v>
+      </c>
+      <c r="J70">
+        <v>9</v>
+      </c>
+      <c r="K70">
+        <v>9</v>
+      </c>
+      <c r="L70">
+        <v>7</v>
+      </c>
     </row>
     <row r="71" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B71">
@@ -2509,6 +2692,33 @@
       <c r="C71">
         <v>8</v>
       </c>
+      <c r="D71">
+        <v>8</v>
+      </c>
+      <c r="E71">
+        <v>8</v>
+      </c>
+      <c r="F71">
+        <v>6</v>
+      </c>
+      <c r="G71">
+        <v>8</v>
+      </c>
+      <c r="H71">
+        <v>6</v>
+      </c>
+      <c r="I71">
+        <v>7</v>
+      </c>
+      <c r="J71">
+        <v>7</v>
+      </c>
+      <c r="K71">
+        <v>8</v>
+      </c>
+      <c r="L71">
+        <v>7</v>
+      </c>
     </row>
     <row r="72" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B72">
@@ -2517,6 +2727,33 @@
       <c r="C72">
         <v>6</v>
       </c>
+      <c r="D72">
+        <v>6</v>
+      </c>
+      <c r="E72">
+        <v>5</v>
+      </c>
+      <c r="F72">
+        <v>4</v>
+      </c>
+      <c r="G72">
+        <v>6</v>
+      </c>
+      <c r="H72">
+        <v>6</v>
+      </c>
+      <c r="I72">
+        <v>6</v>
+      </c>
+      <c r="J72">
+        <v>4</v>
+      </c>
+      <c r="K72">
+        <v>4</v>
+      </c>
+      <c r="L72">
+        <v>6</v>
+      </c>
     </row>
     <row r="73" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B73">
@@ -2525,6 +2762,33 @@
       <c r="C73">
         <v>8</v>
       </c>
+      <c r="D73">
+        <v>8</v>
+      </c>
+      <c r="E73">
+        <v>7</v>
+      </c>
+      <c r="F73">
+        <v>7</v>
+      </c>
+      <c r="G73">
+        <v>5</v>
+      </c>
+      <c r="H73">
+        <v>6</v>
+      </c>
+      <c r="I73">
+        <v>8</v>
+      </c>
+      <c r="J73">
+        <v>8</v>
+      </c>
+      <c r="K73">
+        <v>8</v>
+      </c>
+      <c r="L73">
+        <v>7</v>
+      </c>
     </row>
     <row r="74" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B74">
@@ -2533,6 +2797,33 @@
       <c r="C74">
         <v>12</v>
       </c>
+      <c r="D74">
+        <v>12</v>
+      </c>
+      <c r="E74">
+        <v>11</v>
+      </c>
+      <c r="F74">
+        <v>11</v>
+      </c>
+      <c r="G74">
+        <v>11</v>
+      </c>
+      <c r="H74">
+        <v>8</v>
+      </c>
+      <c r="I74">
+        <v>8</v>
+      </c>
+      <c r="J74">
+        <v>11</v>
+      </c>
+      <c r="K74">
+        <v>11</v>
+      </c>
+      <c r="L74">
+        <v>10</v>
+      </c>
     </row>
     <row r="75" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B75">
@@ -2541,6 +2832,33 @@
       <c r="C75">
         <v>7</v>
       </c>
+      <c r="D75">
+        <v>4</v>
+      </c>
+      <c r="E75">
+        <v>7</v>
+      </c>
+      <c r="F75">
+        <v>5</v>
+      </c>
+      <c r="G75">
+        <v>1</v>
+      </c>
+      <c r="H75">
+        <v>4</v>
+      </c>
+      <c r="I75">
+        <v>5</v>
+      </c>
+      <c r="J75">
+        <v>6</v>
+      </c>
+      <c r="K75">
+        <v>6</v>
+      </c>
+      <c r="L75">
+        <v>4</v>
+      </c>
     </row>
     <row r="76" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B76">
@@ -2549,6 +2867,33 @@
       <c r="C76">
         <v>6</v>
       </c>
+      <c r="D76">
+        <v>6</v>
+      </c>
+      <c r="E76">
+        <v>6</v>
+      </c>
+      <c r="F76">
+        <v>3</v>
+      </c>
+      <c r="G76">
+        <v>1</v>
+      </c>
+      <c r="H76">
+        <v>3</v>
+      </c>
+      <c r="I76">
+        <v>4</v>
+      </c>
+      <c r="J76">
+        <v>5</v>
+      </c>
+      <c r="K76">
+        <v>6</v>
+      </c>
+      <c r="L76">
+        <v>6</v>
+      </c>
     </row>
     <row r="77" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B77">
@@ -2556,6 +2901,33 @@
       </c>
       <c r="C77">
         <v>10</v>
+      </c>
+      <c r="D77">
+        <v>10</v>
+      </c>
+      <c r="E77">
+        <v>8</v>
+      </c>
+      <c r="F77">
+        <v>8</v>
+      </c>
+      <c r="G77">
+        <v>10</v>
+      </c>
+      <c r="H77">
+        <v>4</v>
+      </c>
+      <c r="I77">
+        <v>7</v>
+      </c>
+      <c r="J77">
+        <v>4</v>
+      </c>
+      <c r="K77">
+        <v>10</v>
+      </c>
+      <c r="L77">
+        <v>3</v>
       </c>
     </row>
     <row r="78" spans="2:12" x14ac:dyDescent="0.2">
@@ -2565,6 +2937,33 @@
       <c r="C78">
         <v>7</v>
       </c>
+      <c r="D78">
+        <v>7</v>
+      </c>
+      <c r="E78">
+        <v>7</v>
+      </c>
+      <c r="F78">
+        <v>7</v>
+      </c>
+      <c r="G78">
+        <v>7</v>
+      </c>
+      <c r="H78">
+        <v>4</v>
+      </c>
+      <c r="I78">
+        <v>4</v>
+      </c>
+      <c r="J78">
+        <v>7</v>
+      </c>
+      <c r="K78">
+        <v>7</v>
+      </c>
+      <c r="L78">
+        <v>6</v>
+      </c>
     </row>
     <row r="79" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B79">
@@ -2573,6 +2972,33 @@
       <c r="C79">
         <v>6</v>
       </c>
+      <c r="D79">
+        <v>6</v>
+      </c>
+      <c r="E79">
+        <v>6</v>
+      </c>
+      <c r="F79">
+        <v>6</v>
+      </c>
+      <c r="G79">
+        <v>4</v>
+      </c>
+      <c r="H79">
+        <v>4</v>
+      </c>
+      <c r="I79">
+        <v>6</v>
+      </c>
+      <c r="J79">
+        <v>4</v>
+      </c>
+      <c r="K79">
+        <v>6</v>
+      </c>
+      <c r="L79">
+        <v>6</v>
+      </c>
     </row>
     <row r="80" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B80" t="s">
@@ -2581,6 +3007,9 @@
       <c r="D80">
         <v>5</v>
       </c>
+      <c r="E80">
+        <v>5</v>
+      </c>
       <c r="F80">
         <v>5</v>
       </c>
@@ -2591,6 +3020,9 @@
         <v>5</v>
       </c>
       <c r="I80">
+        <v>5</v>
+      </c>
+      <c r="J80">
         <v>5</v>
       </c>
       <c r="K80">
@@ -2609,40 +3041,69 @@
         <v>100</v>
       </c>
       <c r="D81">
-        <f t="shared" ref="D81:F81" si="10">SUM(D68:D80)</f>
-        <v>5</v>
+        <f t="shared" ref="D81:L83" si="10">SUM(D68:D79)</f>
+        <v>92</v>
       </c>
       <c r="E81">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="F81">
         <f t="shared" si="10"/>
-        <v>5</v>
+        <v>84</v>
       </c>
       <c r="G81">
-        <f>SUM(G68:G80)</f>
-        <v>5</v>
+        <f t="shared" si="10"/>
+        <v>74</v>
       </c>
       <c r="H81">
-        <f t="shared" ref="H81:L81" si="11">SUM(H68:H80)</f>
-        <v>5</v>
+        <f t="shared" si="10"/>
+        <v>68</v>
       </c>
       <c r="I81">
-        <f t="shared" si="11"/>
-        <v>5</v>
+        <f t="shared" si="10"/>
+        <v>81</v>
       </c>
       <c r="J81">
-        <f t="shared" si="11"/>
-        <v>0</v>
+        <f t="shared" si="10"/>
+        <v>85</v>
       </c>
       <c r="K81">
-        <f t="shared" si="11"/>
-        <v>5</v>
+        <f t="shared" si="10"/>
+        <v>95</v>
       </c>
       <c r="L81">
-        <f t="shared" si="11"/>
-        <v>5</v>
+        <f t="shared" si="10"/>
+        <v>78</v>
+      </c>
+    </row>
+    <row r="83" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="D83">
+        <v>92</v>
+      </c>
+      <c r="E83">
+        <v>90</v>
+      </c>
+      <c r="F83">
+        <v>84</v>
+      </c>
+      <c r="G83">
+        <v>74</v>
+      </c>
+      <c r="H83">
+        <v>68</v>
+      </c>
+      <c r="I83">
+        <v>81</v>
+      </c>
+      <c r="J83">
+        <v>85</v>
+      </c>
+      <c r="K83">
+        <v>95</v>
+      </c>
+      <c r="L83">
+        <v>78</v>
       </c>
     </row>
   </sheetData>
